--- a/research/traditional_assets/database/data/hong_kong/hong_kong_software_internet.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_software_internet.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1106941742842276</v>
+        <v>0.1105491038966586</v>
       </c>
       <c r="C2">
-        <v>4089.902134793277</v>
+        <v>4055.344393837789</v>
       </c>
       <c r="D2">
-        <v>4026.002134793277</v>
+        <v>4035.022393837789</v>
       </c>
       <c r="E2">
-        <v>-2126.4</v>
+        <v>-2082.822</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>43.578</v>
       </c>
       <c r="G2">
         <v>63.9</v>
@@ -1585,28 +1585,28 @@
         <v>162.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.1919734</v>
       </c>
       <c r="N2">
-        <v>162.1</v>
+        <v>159.9080266</v>
       </c>
       <c r="O2">
-        <v>26.7465</v>
+        <v>26.384824389</v>
       </c>
       <c r="P2">
-        <v>135.3535</v>
+        <v>133.523202211</v>
       </c>
       <c r="Q2">
-        <v>182.0535</v>
+        <v>180.223202211</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1106941742842276</v>
+        <v>0.1112415140370289</v>
       </c>
       <c r="T2">
-        <v>1.264908244262672</v>
+        <v>1.275576914807716</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>73.95162733270394</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1105491038966586</v>
+        <v>0.1104040335090896</v>
       </c>
       <c r="C3">
-        <v>4055.344393837789</v>
+        <v>4020.827163432636</v>
       </c>
       <c r="D3">
-        <v>4035.022393837789</v>
+        <v>4044.083163432636</v>
       </c>
       <c r="E3">
-        <v>-2082.822</v>
+        <v>-2039.244</v>
       </c>
       <c r="F3">
-        <v>43.578</v>
+        <v>87.15600000000001</v>
       </c>
       <c r="G3">
         <v>63.9</v>
@@ -1667,28 +1667,28 @@
         <v>162.1</v>
       </c>
       <c r="M3">
-        <v>2.1919734</v>
+        <v>4.3839468</v>
       </c>
       <c r="N3">
-        <v>159.9080266</v>
+        <v>157.7160532</v>
       </c>
       <c r="O3">
-        <v>26.384824389</v>
+        <v>26.023148778</v>
       </c>
       <c r="P3">
-        <v>133.523202211</v>
+        <v>131.692904422</v>
       </c>
       <c r="Q3">
-        <v>180.223202211</v>
+        <v>178.392904422</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1112415140370289</v>
+        <v>0.111800023988867</v>
       </c>
       <c r="T3">
-        <v>1.275576914807716</v>
+        <v>1.286463313323067</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>73.95162733270394</v>
+        <v>36.97581366635197</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1104040335090896</v>
+        <v>0.1102589631215207</v>
       </c>
       <c r="C4">
-        <v>4020.827163432636</v>
+        <v>3986.350717095146</v>
       </c>
       <c r="D4">
-        <v>4044.083163432636</v>
+        <v>4053.184717095146</v>
       </c>
       <c r="E4">
-        <v>-2039.244</v>
+        <v>-1995.666</v>
       </c>
       <c r="F4">
-        <v>87.15600000000001</v>
+        <v>130.734</v>
       </c>
       <c r="G4">
         <v>63.9</v>
@@ -1749,28 +1749,28 @@
         <v>162.1</v>
       </c>
       <c r="M4">
-        <v>4.3839468</v>
+        <v>6.575920200000001</v>
       </c>
       <c r="N4">
-        <v>157.7160532</v>
+        <v>155.5240798</v>
       </c>
       <c r="O4">
-        <v>26.023148778</v>
+        <v>25.661473167</v>
       </c>
       <c r="P4">
-        <v>131.692904422</v>
+        <v>129.862606633</v>
       </c>
       <c r="Q4">
-        <v>178.392904422</v>
+        <v>176.562606633</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.111800023988867</v>
+        <v>0.1123700496098151</v>
       </c>
       <c r="T4">
-        <v>1.286463313323067</v>
+        <v>1.297574173663477</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.97581366635197</v>
+        <v>24.65054244423465</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1102589631215207</v>
+        <v>0.1101138927339517</v>
       </c>
       <c r="C5">
-        <v>3986.350717095146</v>
+        <v>3951.915330810507</v>
       </c>
       <c r="D5">
-        <v>4053.184717095146</v>
+        <v>4062.327330810507</v>
       </c>
       <c r="E5">
-        <v>-1995.666</v>
+        <v>-1952.088</v>
       </c>
       <c r="F5">
-        <v>130.734</v>
+        <v>174.312</v>
       </c>
       <c r="G5">
         <v>63.9</v>
@@ -1831,28 +1831,28 @@
         <v>162.1</v>
       </c>
       <c r="M5">
-        <v>6.575920200000001</v>
+        <v>8.767893600000001</v>
       </c>
       <c r="N5">
-        <v>155.5240798</v>
+        <v>153.3321064</v>
       </c>
       <c r="O5">
-        <v>25.661473167</v>
+        <v>25.299797556</v>
       </c>
       <c r="P5">
-        <v>129.862606633</v>
+        <v>128.032308844</v>
       </c>
       <c r="Q5">
-        <v>176.562606633</v>
+        <v>174.732308844</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1123700496098151</v>
+        <v>0.112951950764533</v>
       </c>
       <c r="T5">
-        <v>1.297574173663477</v>
+        <v>1.308916510260978</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.65054244423465</v>
+        <v>18.48790683317598</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1101138927339517</v>
+        <v>0.1099688223463827</v>
       </c>
       <c r="C6">
-        <v>3951.915330810507</v>
+        <v>3917.521283059645</v>
       </c>
       <c r="D6">
-        <v>4062.327330810507</v>
+        <v>4071.511283059645</v>
       </c>
       <c r="E6">
-        <v>-1952.088</v>
+        <v>-1908.51</v>
       </c>
       <c r="F6">
-        <v>174.312</v>
+        <v>217.89</v>
       </c>
       <c r="G6">
         <v>63.9</v>
@@ -1913,28 +1913,28 @@
         <v>162.1</v>
       </c>
       <c r="M6">
-        <v>8.767893600000001</v>
+        <v>10.959867</v>
       </c>
       <c r="N6">
-        <v>153.3321064</v>
+        <v>151.140133</v>
       </c>
       <c r="O6">
-        <v>25.299797556</v>
+        <v>24.938121945</v>
       </c>
       <c r="P6">
-        <v>128.032308844</v>
+        <v>126.202011055</v>
       </c>
       <c r="Q6">
-        <v>174.732308844</v>
+        <v>172.902011055</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.112951950764533</v>
+        <v>0.1135461024698766</v>
       </c>
       <c r="T6">
-        <v>1.308916510260978</v>
+        <v>1.320497632892111</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.48790683317598</v>
+        <v>14.79032546654079</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1099688223463827</v>
+        <v>0.1098989019588137</v>
       </c>
       <c r="C7">
-        <v>3917.521283059645</v>
+        <v>3878.384570479609</v>
       </c>
       <c r="D7">
-        <v>4071.511283059645</v>
+        <v>4075.952570479608</v>
       </c>
       <c r="E7">
-        <v>-1908.51</v>
+        <v>-1864.932</v>
       </c>
       <c r="F7">
-        <v>217.89</v>
+        <v>261.468</v>
       </c>
       <c r="G7">
         <v>63.9</v>
@@ -1995,45 +1995,45 @@
         <v>162.1</v>
       </c>
       <c r="M7">
-        <v>10.959867</v>
+        <v>13.5440424</v>
       </c>
       <c r="N7">
-        <v>151.140133</v>
+        <v>148.5559576</v>
       </c>
       <c r="O7">
-        <v>24.938121945</v>
+        <v>24.511733004</v>
       </c>
       <c r="P7">
-        <v>126.202011055</v>
+        <v>124.044224596</v>
       </c>
       <c r="Q7">
-        <v>172.902011055</v>
+        <v>170.744224596</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1135461024698766</v>
+        <v>0.1141528957008657</v>
       </c>
       <c r="T7">
-        <v>1.320497632892111</v>
+        <v>1.332325162387736</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.165</v>
       </c>
       <c r="W7">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.79032546654079</v>
+        <v>11.96836182379346</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1098989019588137</v>
+        <v>0.1097663565712448</v>
       </c>
       <c r="C8">
-        <v>3878.384570479609</v>
+        <v>3843.252396412577</v>
       </c>
       <c r="D8">
-        <v>4075.952570479608</v>
+        <v>4084.398396412577</v>
       </c>
       <c r="E8">
-        <v>-1864.932</v>
+        <v>-1821.354</v>
       </c>
       <c r="F8">
-        <v>261.468</v>
+        <v>305.046</v>
       </c>
       <c r="G8">
         <v>63.9</v>
@@ -2077,28 +2077,28 @@
         <v>162.1</v>
       </c>
       <c r="M8">
-        <v>13.5440424</v>
+        <v>15.8013828</v>
       </c>
       <c r="N8">
-        <v>148.5559576</v>
+        <v>146.2986172</v>
       </c>
       <c r="O8">
-        <v>24.511733004</v>
+        <v>24.139271838</v>
       </c>
       <c r="P8">
-        <v>124.044224596</v>
+        <v>122.159345362</v>
       </c>
       <c r="Q8">
-        <v>170.744224596</v>
+        <v>168.859345362</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1141528957008657</v>
+        <v>0.1147727382486503</v>
       </c>
       <c r="T8">
-        <v>1.332325162387736</v>
+        <v>1.344407047356385</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.96836182379346</v>
+        <v>10.25859584896583</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1097663565712448</v>
+        <v>0.1097473711836758</v>
       </c>
       <c r="C9">
-        <v>3843.252396412576</v>
+        <v>3800.887016808172</v>
       </c>
       <c r="D9">
-        <v>4084.398396412576</v>
+        <v>4085.611016808172</v>
       </c>
       <c r="E9">
-        <v>-1821.354</v>
+        <v>-1777.776</v>
       </c>
       <c r="F9">
-        <v>305.046</v>
+        <v>348.624</v>
       </c>
       <c r="G9">
         <v>63.9</v>
@@ -2159,45 +2159,45 @@
         <v>162.1</v>
       </c>
       <c r="M9">
-        <v>15.8013828</v>
+        <v>18.651384</v>
       </c>
       <c r="N9">
-        <v>146.2986172</v>
+        <v>143.448616</v>
       </c>
       <c r="O9">
-        <v>24.139271838</v>
+        <v>23.66902164</v>
       </c>
       <c r="P9">
-        <v>122.159345362</v>
+        <v>119.77959436</v>
       </c>
       <c r="Q9">
-        <v>168.859345362</v>
+        <v>166.47959436</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1147727382486503</v>
+        <v>0.1154060556344302</v>
       </c>
       <c r="T9">
-        <v>1.344407047356386</v>
+        <v>1.356751581998267</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.165</v>
       </c>
       <c r="W9">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.25859584896582</v>
+        <v>8.691044053352822</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1097473711836758</v>
+        <v>0.1096290207961068</v>
       </c>
       <c r="C10">
-        <v>3800.887016808172</v>
+        <v>3764.884468244909</v>
       </c>
       <c r="D10">
-        <v>4085.611016808172</v>
+        <v>4093.186468244909</v>
       </c>
       <c r="E10">
-        <v>-1777.776</v>
+        <v>-1734.198</v>
       </c>
       <c r="F10">
-        <v>348.624</v>
+        <v>392.202</v>
       </c>
       <c r="G10">
         <v>63.9</v>
@@ -2241,28 +2241,28 @@
         <v>162.1</v>
       </c>
       <c r="M10">
-        <v>18.651384</v>
+        <v>20.982807</v>
       </c>
       <c r="N10">
-        <v>143.448616</v>
+        <v>141.117193</v>
       </c>
       <c r="O10">
-        <v>23.66902164</v>
+        <v>23.284336845</v>
       </c>
       <c r="P10">
-        <v>119.77959436</v>
+        <v>117.832856155</v>
       </c>
       <c r="Q10">
-        <v>166.47959436</v>
+        <v>164.532856155</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1154060556344302</v>
+        <v>0.1160532920836339</v>
       </c>
       <c r="T10">
-        <v>1.356751581998267</v>
+        <v>1.369367425093815</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.691044053352822</v>
+        <v>7.725372491869176</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1096290207961068</v>
+        <v>0.1095774704085378</v>
       </c>
       <c r="C11">
-        <v>3764.884468244909</v>
+        <v>3724.614930425651</v>
       </c>
       <c r="D11">
-        <v>4093.186468244909</v>
+        <v>4096.494930425652</v>
       </c>
       <c r="E11">
-        <v>-1734.198</v>
+        <v>-1690.62</v>
       </c>
       <c r="F11">
-        <v>392.202</v>
+        <v>435.78</v>
       </c>
       <c r="G11">
         <v>63.9</v>
@@ -2323,45 +2323,45 @@
         <v>162.1</v>
       </c>
       <c r="M11">
-        <v>20.982807</v>
+        <v>23.662854</v>
       </c>
       <c r="N11">
-        <v>141.117193</v>
+        <v>138.437146</v>
       </c>
       <c r="O11">
-        <v>23.284336845</v>
+        <v>22.84212909</v>
       </c>
       <c r="P11">
-        <v>117.832856155</v>
+        <v>115.59501691</v>
       </c>
       <c r="Q11">
-        <v>164.532856155</v>
+        <v>162.29501691</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1160532920836339</v>
+        <v>0.116714911565042</v>
       </c>
       <c r="T11">
-        <v>1.369367425093815</v>
+        <v>1.382263620258154</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.165</v>
       </c>
       <c r="W11">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.725372491869176</v>
+        <v>6.850399364337032</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1095774704085378</v>
+        <v>0.1094658000209689</v>
       </c>
       <c r="C12">
-        <v>3724.614930425651</v>
+        <v>3688.222219488292</v>
       </c>
       <c r="D12">
-        <v>4096.494930425652</v>
+        <v>4103.680219488293</v>
       </c>
       <c r="E12">
-        <v>-1690.62</v>
+        <v>-1647.042</v>
       </c>
       <c r="F12">
-        <v>435.78</v>
+        <v>479.358</v>
       </c>
       <c r="G12">
         <v>63.9</v>
@@ -2405,28 +2405,28 @@
         <v>162.1</v>
       </c>
       <c r="M12">
-        <v>23.662854</v>
+        <v>26.0291394</v>
       </c>
       <c r="N12">
-        <v>138.437146</v>
+        <v>136.0708606</v>
       </c>
       <c r="O12">
-        <v>22.84212909</v>
+        <v>22.451691999</v>
       </c>
       <c r="P12">
-        <v>115.59501691</v>
+        <v>113.619168601</v>
       </c>
       <c r="Q12">
-        <v>162.29501691</v>
+        <v>160.319168601</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.116714911565042</v>
+        <v>0.117391398899965</v>
       </c>
       <c r="T12">
-        <v>1.382263620258154</v>
+        <v>1.395449617561017</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.850399364337031</v>
+        <v>6.227635785760938</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1094658000209689</v>
+        <v>0.1094543296333999</v>
       </c>
       <c r="C13">
-        <v>3688.222219488292</v>
+        <v>3645.383694758045</v>
       </c>
       <c r="D13">
-        <v>4103.680219488293</v>
+        <v>4104.419694758046</v>
       </c>
       <c r="E13">
-        <v>-1647.042</v>
+        <v>-1603.464</v>
       </c>
       <c r="F13">
-        <v>479.358</v>
+        <v>522.936</v>
       </c>
       <c r="G13">
         <v>63.9</v>
@@ -2487,45 +2487,45 @@
         <v>162.1</v>
       </c>
       <c r="M13">
-        <v>26.0291394</v>
+        <v>28.9183608</v>
       </c>
       <c r="N13">
-        <v>136.0708606</v>
+        <v>133.1816392</v>
       </c>
       <c r="O13">
-        <v>22.451691999</v>
+        <v>21.974970468</v>
       </c>
       <c r="P13">
-        <v>113.619168601</v>
+        <v>111.206668732</v>
       </c>
       <c r="Q13">
-        <v>160.319168601</v>
+        <v>157.906668732</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.117391398899965</v>
+        <v>0.1180832609470453</v>
       </c>
       <c r="T13">
-        <v>1.395449617561017</v>
+        <v>1.408935296620763</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.165</v>
       </c>
       <c r="W13">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.227635785760938</v>
+        <v>5.605435284561495</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1094543296333999</v>
+        <v>0.1093510092458309</v>
       </c>
       <c r="C14">
-        <v>3645.383694758045</v>
+        <v>3608.478605835946</v>
       </c>
       <c r="D14">
-        <v>4104.419694758046</v>
+        <v>4111.092605835946</v>
       </c>
       <c r="E14">
-        <v>-1603.464</v>
+        <v>-1559.886</v>
       </c>
       <c r="F14">
-        <v>522.936</v>
+        <v>566.514</v>
       </c>
       <c r="G14">
         <v>63.9</v>
@@ -2569,28 +2569,28 @@
         <v>162.1</v>
       </c>
       <c r="M14">
-        <v>28.9183608</v>
+        <v>31.3282242</v>
       </c>
       <c r="N14">
-        <v>133.1816392</v>
+        <v>130.7717758</v>
       </c>
       <c r="O14">
-        <v>21.974970468</v>
+        <v>21.577343007</v>
       </c>
       <c r="P14">
-        <v>111.206668732</v>
+        <v>109.194432793</v>
       </c>
       <c r="Q14">
-        <v>157.906668732</v>
+        <v>155.894432793</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1180832609470453</v>
+        <v>0.1187910278687712</v>
       </c>
       <c r="T14">
-        <v>1.408935296620763</v>
+        <v>1.422730991291078</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.605435284561495</v>
+        <v>5.174247954979842</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1093510092458309</v>
+        <v>0.1092476888582619</v>
       </c>
       <c r="C15">
-        <v>3608.478605835946</v>
+        <v>3571.595249707305</v>
       </c>
       <c r="D15">
-        <v>4111.092605835946</v>
+        <v>4117.787249707306</v>
       </c>
       <c r="E15">
-        <v>-1559.886</v>
+        <v>-1516.308</v>
       </c>
       <c r="F15">
-        <v>566.514</v>
+        <v>610.0920000000001</v>
       </c>
       <c r="G15">
         <v>63.9</v>
@@ -2651,28 +2651,28 @@
         <v>162.1</v>
       </c>
       <c r="M15">
-        <v>31.3282242</v>
+        <v>33.73808760000001</v>
       </c>
       <c r="N15">
-        <v>130.7717758</v>
+        <v>128.3619124</v>
       </c>
       <c r="O15">
-        <v>21.577343007</v>
+        <v>21.179715546</v>
       </c>
       <c r="P15">
-        <v>109.194432793</v>
+        <v>107.182196854</v>
       </c>
       <c r="Q15">
-        <v>155.894432793</v>
+        <v>153.882196854</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1187910278687712</v>
+        <v>0.1195152544863511</v>
       </c>
       <c r="T15">
-        <v>1.422730991291078</v>
+        <v>1.436847516070005</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.174247954979842</v>
+        <v>4.804658815338424</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1092476888582619</v>
+        <v>0.109457493470693</v>
       </c>
       <c r="C16">
-        <v>3571.595249707305</v>
+        <v>3514.445701239157</v>
       </c>
       <c r="D16">
-        <v>4117.787249707306</v>
+        <v>4104.215701239157</v>
       </c>
       <c r="E16">
-        <v>-1516.308</v>
+        <v>-1472.73</v>
       </c>
       <c r="F16">
-        <v>610.0920000000001</v>
+        <v>653.6700000000001</v>
       </c>
       <c r="G16">
         <v>63.9</v>
@@ -2733,45 +2733,45 @@
         <v>162.1</v>
       </c>
       <c r="M16">
-        <v>33.73808760000001</v>
+        <v>37.78212600000001</v>
       </c>
       <c r="N16">
-        <v>128.3619124</v>
+        <v>124.317874</v>
       </c>
       <c r="O16">
-        <v>21.179715546</v>
+        <v>20.51244921</v>
       </c>
       <c r="P16">
-        <v>107.182196854</v>
+        <v>103.80542479</v>
       </c>
       <c r="Q16">
-        <v>153.882196854</v>
+        <v>150.50542479</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1195152544863511</v>
+        <v>0.120256521730227</v>
       </c>
       <c r="T16">
-        <v>1.436847516070005</v>
+        <v>1.451296194373143</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.804658815338424</v>
+        <v>4.290388529221462</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.109457493470693</v>
+        <v>0.109375048083124</v>
       </c>
       <c r="C17">
-        <v>3514.445701239158</v>
+        <v>3476.190129839022</v>
       </c>
       <c r="D17">
-        <v>4104.215701239158</v>
+        <v>4109.538129839022</v>
       </c>
       <c r="E17">
-        <v>-1472.73</v>
+        <v>-1429.152</v>
       </c>
       <c r="F17">
-        <v>653.67</v>
+        <v>697.248</v>
       </c>
       <c r="G17">
         <v>63.9</v>
@@ -2815,28 +2815,28 @@
         <v>162.1</v>
       </c>
       <c r="M17">
-        <v>37.782126</v>
+        <v>40.3009344</v>
       </c>
       <c r="N17">
-        <v>124.317874</v>
+        <v>121.7990656</v>
       </c>
       <c r="O17">
-        <v>20.51244921</v>
+        <v>20.096845824</v>
       </c>
       <c r="P17">
-        <v>103.80542479</v>
+        <v>101.702219776</v>
       </c>
       <c r="Q17">
-        <v>150.50542479</v>
+        <v>148.402219776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.120256521730227</v>
+        <v>0.1210154381941952</v>
       </c>
       <c r="T17">
-        <v>1.451296194373143</v>
+        <v>1.466088888826355</v>
       </c>
       <c r="U17">
         <v>0.0578</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.290388529221463</v>
+        <v>4.022239246145121</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.109375048083124</v>
+        <v>0.109789427695555</v>
       </c>
       <c r="C18">
-        <v>3476.190129839022</v>
+        <v>3405.999783411808</v>
       </c>
       <c r="D18">
-        <v>4109.538129839022</v>
+        <v>4082.925783411809</v>
       </c>
       <c r="E18">
-        <v>-1429.152</v>
+        <v>-1385.574</v>
       </c>
       <c r="F18">
-        <v>697.248</v>
+        <v>740.8260000000001</v>
       </c>
       <c r="G18">
         <v>63.9</v>
@@ -2897,45 +2897,45 @@
         <v>162.1</v>
       </c>
       <c r="M18">
-        <v>40.3009344</v>
+        <v>45.41263380000001</v>
       </c>
       <c r="N18">
-        <v>121.7990656</v>
+        <v>116.6873662</v>
       </c>
       <c r="O18">
-        <v>20.096845824</v>
+        <v>19.253415423</v>
       </c>
       <c r="P18">
-        <v>101.702219776</v>
+        <v>97.43395077699998</v>
       </c>
       <c r="Q18">
-        <v>148.402219776</v>
+        <v>144.133950777</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1210154381941952</v>
+        <v>0.1217926418018735</v>
       </c>
       <c r="T18">
-        <v>1.466088888826355</v>
+        <v>1.481238033748319</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.165</v>
       </c>
       <c r="W18">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.022239246145121</v>
+        <v>3.569491272272342</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.109789427695555</v>
+        <v>0.110157047307986</v>
       </c>
       <c r="C19">
-        <v>3405.999783411808</v>
+        <v>3339.099339998588</v>
       </c>
       <c r="D19">
-        <v>4082.925783411809</v>
+        <v>4059.603339998588</v>
       </c>
       <c r="E19">
-        <v>-1385.574</v>
+        <v>-1341.996</v>
       </c>
       <c r="F19">
-        <v>740.8260000000001</v>
+        <v>784.4040000000001</v>
       </c>
       <c r="G19">
         <v>63.9</v>
@@ -2979,45 +2979,45 @@
         <v>162.1</v>
       </c>
       <c r="M19">
-        <v>45.41263380000001</v>
+        <v>50.28029640000001</v>
       </c>
       <c r="N19">
-        <v>116.6873662</v>
+        <v>111.8197036</v>
       </c>
       <c r="O19">
-        <v>19.253415423</v>
+        <v>18.450251094</v>
       </c>
       <c r="P19">
-        <v>97.43395077699998</v>
+        <v>93.36945250599999</v>
       </c>
       <c r="Q19">
-        <v>144.133950777</v>
+        <v>140.069452506</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1217926418018735</v>
+        <v>0.1225888015951049</v>
       </c>
       <c r="T19">
-        <v>1.481238033748319</v>
+        <v>1.496756670009843</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.569491272272342</v>
+        <v>3.223926897932924</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1101570473079861</v>
+        <v>0.1101272069204171</v>
       </c>
       <c r="C20">
-        <v>3339.099339998586</v>
+        <v>3297.404526644507</v>
       </c>
       <c r="D20">
-        <v>4059.603339998586</v>
+        <v>4061.486526644508</v>
       </c>
       <c r="E20">
-        <v>-1341.996</v>
+        <v>-1298.418</v>
       </c>
       <c r="F20">
-        <v>784.404</v>
+        <v>827.9820000000001</v>
       </c>
       <c r="G20">
         <v>63.9</v>
@@ -3061,28 +3061,28 @@
         <v>162.1</v>
       </c>
       <c r="M20">
-        <v>50.2802964</v>
+        <v>53.07364620000001</v>
       </c>
       <c r="N20">
-        <v>111.8197036</v>
+        <v>109.0263538</v>
       </c>
       <c r="O20">
-        <v>18.450251094</v>
+        <v>17.989348377</v>
       </c>
       <c r="P20">
-        <v>93.369452506</v>
+        <v>91.03700542299998</v>
       </c>
       <c r="Q20">
-        <v>140.069452506</v>
+        <v>137.737005423</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1225888015951049</v>
+        <v>0.1234046196548359</v>
       </c>
       <c r="T20">
-        <v>1.496756670009843</v>
+        <v>1.512658482475355</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.223926897932925</v>
+        <v>3.054246534883823</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1101272069204171</v>
+        <v>0.1113999665328481</v>
       </c>
       <c r="C21">
-        <v>3297.404526644507</v>
+        <v>3175.02624227306</v>
       </c>
       <c r="D21">
-        <v>4061.486526644508</v>
+        <v>3982.68624227306</v>
       </c>
       <c r="E21">
-        <v>-1298.418</v>
+        <v>-1254.84</v>
       </c>
       <c r="F21">
-        <v>827.9820000000001</v>
+        <v>871.5600000000001</v>
       </c>
       <c r="G21">
         <v>63.9</v>
@@ -3143,45 +3143,45 @@
         <v>162.1</v>
       </c>
       <c r="M21">
-        <v>53.07364620000001</v>
+        <v>62.66516400000001</v>
       </c>
       <c r="N21">
-        <v>109.0263538</v>
+        <v>99.43483599999999</v>
       </c>
       <c r="O21">
-        <v>17.989348377</v>
+        <v>16.40674794</v>
       </c>
       <c r="P21">
-        <v>91.03700542299998</v>
+        <v>83.02808805999999</v>
       </c>
       <c r="Q21">
-        <v>137.737005423</v>
+        <v>129.72808806</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1234046196548359</v>
+        <v>0.1242408331660601</v>
       </c>
       <c r="T21">
-        <v>1.512658482475355</v>
+        <v>1.528957840252505</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.165</v>
       </c>
       <c r="W21">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.054246534883823</v>
+        <v>2.586764154961758</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1113999665328481</v>
+        <v>0.1121191211452791</v>
       </c>
       <c r="C22">
-        <v>3175.02624227306</v>
+        <v>3088.260589428234</v>
       </c>
       <c r="D22">
-        <v>3982.68624227306</v>
+        <v>3939.498589428234</v>
       </c>
       <c r="E22">
-        <v>-1254.84</v>
+        <v>-1211.262</v>
       </c>
       <c r="F22">
-        <v>871.5600000000001</v>
+        <v>915.1380000000001</v>
       </c>
       <c r="G22">
         <v>63.9</v>
@@ -3225,45 +3225,45 @@
         <v>162.1</v>
       </c>
       <c r="M22">
-        <v>62.66516400000001</v>
+        <v>69.36746040000001</v>
       </c>
       <c r="N22">
-        <v>99.43483599999999</v>
+        <v>92.73253959999998</v>
       </c>
       <c r="O22">
-        <v>16.40674794</v>
+        <v>15.300869034</v>
       </c>
       <c r="P22">
-        <v>83.02808805999999</v>
+        <v>77.43167056599998</v>
       </c>
       <c r="Q22">
-        <v>129.72808806</v>
+        <v>124.131670566</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1242408331660601</v>
+        <v>0.1250982166395938</v>
       </c>
       <c r="T22">
-        <v>1.528957840252505</v>
+        <v>1.545669839998697</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.586764154961758</v>
+        <v>2.336830540793446</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1121191211452791</v>
+        <v>0.1121869757577101</v>
       </c>
       <c r="C23">
-        <v>3088.260589428234</v>
+        <v>3040.655999168515</v>
       </c>
       <c r="D23">
-        <v>3939.498589428234</v>
+        <v>3935.471999168515</v>
       </c>
       <c r="E23">
-        <v>-1211.262</v>
+        <v>-1167.684</v>
       </c>
       <c r="F23">
-        <v>915.138</v>
+        <v>958.716</v>
       </c>
       <c r="G23">
         <v>63.9</v>
@@ -3307,28 +3307,28 @@
         <v>162.1</v>
       </c>
       <c r="M23">
-        <v>69.36746040000001</v>
+        <v>72.67067280000001</v>
       </c>
       <c r="N23">
-        <v>92.73253959999998</v>
+        <v>89.42932719999999</v>
       </c>
       <c r="O23">
-        <v>15.300869034</v>
+        <v>14.755838988</v>
       </c>
       <c r="P23">
-        <v>77.43167056599998</v>
+        <v>74.673488212</v>
       </c>
       <c r="Q23">
-        <v>124.131670566</v>
+        <v>121.373488212</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1250982166395938</v>
+        <v>0.1259775843047566</v>
       </c>
       <c r="T23">
-        <v>1.545669839998697</v>
+        <v>1.562810352558894</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.336830540793446</v>
+        <v>2.230610970757381</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1121869757577101</v>
+        <v>0.1122548303701412</v>
       </c>
       <c r="C24">
-        <v>3040.655999168515</v>
+        <v>2993.059631718785</v>
       </c>
       <c r="D24">
-        <v>3935.471999168515</v>
+        <v>3931.453631718785</v>
       </c>
       <c r="E24">
-        <v>-1167.684</v>
+        <v>-1124.106</v>
       </c>
       <c r="F24">
-        <v>958.716</v>
+        <v>1002.294</v>
       </c>
       <c r="G24">
         <v>63.9</v>
@@ -3389,28 +3389,28 @@
         <v>162.1</v>
       </c>
       <c r="M24">
-        <v>72.67067280000001</v>
+        <v>75.97388520000001</v>
       </c>
       <c r="N24">
-        <v>89.42932719999999</v>
+        <v>86.12611479999998</v>
       </c>
       <c r="O24">
-        <v>14.755838988</v>
+        <v>14.210808942</v>
       </c>
       <c r="P24">
-        <v>74.673488212</v>
+        <v>71.91530585799998</v>
       </c>
       <c r="Q24">
-        <v>121.373488212</v>
+        <v>118.615305858</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1259775843047566</v>
+        <v>0.126879792688495</v>
       </c>
       <c r="T24">
-        <v>1.562810352558894</v>
+        <v>1.580396073237538</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.230610970757381</v>
+        <v>2.133627885072277</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1122548303701412</v>
+        <v>0.1123226849825722</v>
       </c>
       <c r="C25">
-        <v>2993.059631718785</v>
+        <v>2945.471461916698</v>
       </c>
       <c r="D25">
-        <v>3931.453631718785</v>
+        <v>3927.443461916698</v>
       </c>
       <c r="E25">
-        <v>-1124.106</v>
+        <v>-1080.528</v>
       </c>
       <c r="F25">
-        <v>1002.294</v>
+        <v>1045.872</v>
       </c>
       <c r="G25">
         <v>63.9</v>
@@ -3471,28 +3471,28 @@
         <v>162.1</v>
       </c>
       <c r="M25">
-        <v>75.97388520000001</v>
+        <v>79.27709760000002</v>
       </c>
       <c r="N25">
-        <v>86.12611479999998</v>
+        <v>82.82290239999998</v>
       </c>
       <c r="O25">
-        <v>14.210808942</v>
+        <v>13.665778896</v>
       </c>
       <c r="P25">
-        <v>71.91530585799998</v>
+        <v>69.15712350399998</v>
       </c>
       <c r="Q25">
-        <v>118.615305858</v>
+        <v>115.857123504</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.126879792688495</v>
+        <v>0.1278057433981213</v>
       </c>
       <c r="T25">
-        <v>1.580396073237538</v>
+        <v>1.598444576039303</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.133627885072277</v>
+        <v>2.044726723194265</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1123226849825722</v>
+        <v>0.1153547895950032</v>
       </c>
       <c r="C26">
-        <v>2945.471461916699</v>
+        <v>2730.684268340255</v>
       </c>
       <c r="D26">
-        <v>3927.443461916699</v>
+        <v>3756.234268340254</v>
       </c>
       <c r="E26">
-        <v>-1080.528</v>
+        <v>-1036.95</v>
       </c>
       <c r="F26">
-        <v>1045.872</v>
+        <v>1089.45</v>
       </c>
       <c r="G26">
         <v>63.9</v>
@@ -3553,45 +3553,45 @@
         <v>162.1</v>
       </c>
       <c r="M26">
-        <v>79.27709760000002</v>
+        <v>98.0505</v>
       </c>
       <c r="N26">
-        <v>82.82290239999998</v>
+        <v>64.04949999999999</v>
       </c>
       <c r="O26">
-        <v>13.665778896</v>
+        <v>10.5681675</v>
       </c>
       <c r="P26">
-        <v>69.15712350399998</v>
+        <v>53.48133249999999</v>
       </c>
       <c r="Q26">
-        <v>115.857123504</v>
+        <v>100.1813325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1278057433981213</v>
+        <v>0.128756386126671</v>
       </c>
       <c r="T26">
-        <v>1.598444576039303</v>
+        <v>1.616974372249116</v>
       </c>
       <c r="U26">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V26">
         <v>0.165</v>
       </c>
       <c r="W26">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.044726723194265</v>
+        <v>1.653229713260004</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1153547895950032</v>
+        <v>0.1155412142074342</v>
       </c>
       <c r="C27">
-        <v>2730.684268340255</v>
+        <v>2677.065512301901</v>
       </c>
       <c r="D27">
-        <v>3756.234268340254</v>
+        <v>3746.193512301901</v>
       </c>
       <c r="E27">
-        <v>-1036.95</v>
+        <v>-993.3720000000001</v>
       </c>
       <c r="F27">
-        <v>1089.45</v>
+        <v>1133.028</v>
       </c>
       <c r="G27">
         <v>63.9</v>
@@ -3635,28 +3635,28 @@
         <v>162.1</v>
       </c>
       <c r="M27">
-        <v>98.0505</v>
+        <v>101.97252</v>
       </c>
       <c r="N27">
-        <v>64.04949999999999</v>
+        <v>60.12747999999999</v>
       </c>
       <c r="O27">
-        <v>10.5681675</v>
+        <v>9.921034199999999</v>
       </c>
       <c r="P27">
-        <v>53.48133249999999</v>
+        <v>50.20644579999999</v>
       </c>
       <c r="Q27">
-        <v>100.1813325</v>
+        <v>96.9064458</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.128756386126671</v>
+        <v>0.1297327219019381</v>
       </c>
       <c r="T27">
-        <v>1.616974372249116</v>
+        <v>1.636004973761897</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.653229713260004</v>
+        <v>1.589643955057696</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1155412142074342</v>
+        <v>0.1157276388198652</v>
       </c>
       <c r="C28">
-        <v>2677.065512301901</v>
+        <v>2623.500292864655</v>
       </c>
       <c r="D28">
-        <v>3746.193512301901</v>
+        <v>3736.206292864655</v>
       </c>
       <c r="E28">
-        <v>-993.3720000000001</v>
+        <v>-949.7939999999999</v>
       </c>
       <c r="F28">
-        <v>1133.028</v>
+        <v>1176.606</v>
       </c>
       <c r="G28">
         <v>63.9</v>
@@ -3717,28 +3717,28 @@
         <v>162.1</v>
       </c>
       <c r="M28">
-        <v>101.97252</v>
+        <v>105.89454</v>
       </c>
       <c r="N28">
-        <v>60.12747999999999</v>
+        <v>56.20545999999997</v>
       </c>
       <c r="O28">
-        <v>9.921034199999999</v>
+        <v>9.273900899999996</v>
       </c>
       <c r="P28">
-        <v>50.20644579999999</v>
+        <v>46.93155909999998</v>
       </c>
       <c r="Q28">
-        <v>96.9064458</v>
+        <v>93.6315591</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1297327219019381</v>
+        <v>0.1307358066025551</v>
       </c>
       <c r="T28">
-        <v>1.636004973761897</v>
+        <v>1.655556961617494</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.589643955057696</v>
+        <v>1.530768253018522</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1157276388198652</v>
+        <v>0.1301233745211089</v>
       </c>
       <c r="C29">
-        <v>2623.500292864655</v>
+        <v>1942.074974456653</v>
       </c>
       <c r="D29">
-        <v>3736.206292864655</v>
+        <v>3098.358974456653</v>
       </c>
       <c r="E29">
-        <v>-949.7939999999999</v>
+        <v>-906.2159999999999</v>
       </c>
       <c r="F29">
-        <v>1176.606</v>
+        <v>1220.184</v>
       </c>
       <c r="G29">
         <v>63.9</v>
@@ -3799,45 +3799,45 @@
         <v>162.1</v>
       </c>
       <c r="M29">
-        <v>105.89454</v>
+        <v>179.1230112</v>
       </c>
       <c r="N29">
-        <v>56.20545999999997</v>
+        <v>-17.02301120000004</v>
       </c>
       <c r="O29">
-        <v>9.273900899999996</v>
+        <v>-2.808796848000007</v>
       </c>
       <c r="P29">
-        <v>46.93155909999998</v>
+        <v>-14.21421435200003</v>
       </c>
       <c r="Q29">
-        <v>93.6315591</v>
+        <v>32.48578564799998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1307358066025551</v>
+        <v>0.1321624858772037</v>
       </c>
       <c r="T29">
-        <v>1.655556961617494</v>
+        <v>1.683365596157132</v>
       </c>
       <c r="U29">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.165</v>
+        <v>0.1493191735713741</v>
       </c>
       <c r="W29">
-        <v>0.07514999999999999</v>
+        <v>0.1248799453197223</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.530768253018522</v>
+        <v>0.9049646883113585</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1301233745211089</v>
+        <v>0.1311333745211089</v>
       </c>
       <c r="C30">
-        <v>1942.074974456653</v>
+        <v>1861.82500898285</v>
       </c>
       <c r="D30">
-        <v>3098.358974456653</v>
+        <v>3061.68700898285</v>
       </c>
       <c r="E30">
-        <v>-906.2159999999999</v>
+        <v>-862.6379999999999</v>
       </c>
       <c r="F30">
-        <v>1220.184</v>
+        <v>1263.762</v>
       </c>
       <c r="G30">
         <v>63.9</v>
@@ -3881,37 +3881,37 @@
         <v>162.1</v>
       </c>
       <c r="M30">
-        <v>179.1230112</v>
+        <v>185.5202616000001</v>
       </c>
       <c r="N30">
-        <v>-17.02301120000004</v>
+        <v>-23.42026160000006</v>
       </c>
       <c r="O30">
-        <v>-2.808796848000007</v>
+        <v>-3.86434316400001</v>
       </c>
       <c r="P30">
-        <v>-14.21421435200003</v>
+        <v>-19.55591843600005</v>
       </c>
       <c r="Q30">
-        <v>32.48578564799998</v>
+        <v>27.14408156399997</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1321624858772037</v>
+        <v>0.1333788589177277</v>
       </c>
       <c r="T30">
-        <v>1.683365596157132</v>
+        <v>1.707074970750894</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1493191735713741</v>
+        <v>0.1441702365516716</v>
       </c>
       <c r="W30">
-        <v>0.1248799453197223</v>
+        <v>0.1256358092742146</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.9049646883113585</v>
+        <v>0.8737590094040701</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1311333745211089</v>
+        <v>0.1321433745211089</v>
       </c>
       <c r="C31">
-        <v>1861.82500898285</v>
+        <v>1782.432982762267</v>
       </c>
       <c r="D31">
-        <v>3061.68700898285</v>
+        <v>3025.872982762266</v>
       </c>
       <c r="E31">
-        <v>-862.6380000000001</v>
+        <v>-819.0600000000002</v>
       </c>
       <c r="F31">
-        <v>1263.762</v>
+        <v>1307.34</v>
       </c>
       <c r="G31">
         <v>63.9</v>
@@ -3963,37 +3963,37 @@
         <v>162.1</v>
       </c>
       <c r="M31">
-        <v>185.5202616</v>
+        <v>191.917512</v>
       </c>
       <c r="N31">
-        <v>-23.4202616</v>
+        <v>-29.81751200000002</v>
       </c>
       <c r="O31">
-        <v>-3.864343164000001</v>
+        <v>-4.919889480000004</v>
       </c>
       <c r="P31">
-        <v>-19.555918436</v>
+        <v>-24.89762252000002</v>
       </c>
       <c r="Q31">
-        <v>27.14408156400001</v>
+        <v>21.80237748</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1333788589177277</v>
+        <v>0.1346299854736952</v>
       </c>
       <c r="T31">
-        <v>1.707074970750894</v>
+        <v>1.731461756047335</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1441702365516716</v>
+        <v>0.1393645619999492</v>
       </c>
       <c r="W31">
-        <v>0.1256358092742146</v>
+        <v>0.1263412822984075</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8737590094040704</v>
+        <v>0.8446337090906013</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1321433745211089</v>
+        <v>0.1331533745211089</v>
       </c>
       <c r="C32">
-        <v>1782.432982762267</v>
+        <v>1703.869136716315</v>
       </c>
       <c r="D32">
-        <v>3025.872982762266</v>
+        <v>2990.887136716315</v>
       </c>
       <c r="E32">
-        <v>-819.0600000000002</v>
+        <v>-775.482</v>
       </c>
       <c r="F32">
-        <v>1307.34</v>
+        <v>1350.918</v>
       </c>
       <c r="G32">
         <v>63.9</v>
@@ -4045,37 +4045,37 @@
         <v>162.1</v>
       </c>
       <c r="M32">
-        <v>191.917512</v>
+        <v>198.3147624</v>
       </c>
       <c r="N32">
-        <v>-29.81751200000002</v>
+        <v>-36.21476240000004</v>
       </c>
       <c r="O32">
-        <v>-4.919889480000004</v>
+        <v>-5.975435796000007</v>
       </c>
       <c r="P32">
-        <v>-24.89762252000002</v>
+        <v>-30.23932660400003</v>
       </c>
       <c r="Q32">
-        <v>21.80237748</v>
+        <v>16.46067339599998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1346299854736952</v>
+        <v>0.1359173765675169</v>
       </c>
       <c r="T32">
-        <v>1.731461756047335</v>
+        <v>1.756555404685703</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1393645619999492</v>
+        <v>0.1348689309676928</v>
       </c>
       <c r="W32">
-        <v>0.1263412822984075</v>
+        <v>0.1270012409339427</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8446337090906013</v>
+        <v>0.8173874604102592</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1331533745211089</v>
+        <v>0.1521730157583729</v>
       </c>
       <c r="C33">
-        <v>1703.869136716315</v>
+        <v>1125.516411040508</v>
       </c>
       <c r="D33">
-        <v>2990.887136716315</v>
+        <v>2456.112411040508</v>
       </c>
       <c r="E33">
-        <v>-775.482</v>
+        <v>-731.904</v>
       </c>
       <c r="F33">
-        <v>1350.918</v>
+        <v>1394.496</v>
       </c>
       <c r="G33">
         <v>63.9</v>
@@ -4127,45 +4127,45 @@
         <v>162.1</v>
       </c>
       <c r="M33">
-        <v>198.3147624</v>
+        <v>280.0147968000001</v>
       </c>
       <c r="N33">
-        <v>-36.21476240000004</v>
+        <v>-117.9147968000001</v>
       </c>
       <c r="O33">
-        <v>-5.975435796000007</v>
+        <v>-19.45594147200001</v>
       </c>
       <c r="P33">
-        <v>-30.23932660400003</v>
+        <v>-98.45885532800006</v>
       </c>
       <c r="Q33">
-        <v>16.46067339599998</v>
+        <v>-51.75885532800004</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1359173765675169</v>
+        <v>0.1383156339247804</v>
       </c>
       <c r="T33">
-        <v>1.756555404685703</v>
+        <v>1.803301904452839</v>
       </c>
       <c r="U33">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1348689309676928</v>
+        <v>0.09551816655997514</v>
       </c>
       <c r="W33">
-        <v>0.1270012409339427</v>
+        <v>0.181619952154757</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.8173874604102592</v>
+        <v>0.5788979791513644</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1521730157583729</v>
+        <v>0.1537230157583729</v>
       </c>
       <c r="C34">
-        <v>1125.516411040508</v>
+        <v>1046.663505031246</v>
       </c>
       <c r="D34">
-        <v>2456.112411040508</v>
+        <v>2420.837505031246</v>
       </c>
       <c r="E34">
-        <v>-731.904</v>
+        <v>-688.326</v>
       </c>
       <c r="F34">
-        <v>1394.496</v>
+        <v>1438.074</v>
       </c>
       <c r="G34">
         <v>63.9</v>
@@ -4209,37 +4209,37 @@
         <v>162.1</v>
       </c>
       <c r="M34">
-        <v>280.0147968000001</v>
+        <v>288.7652592</v>
       </c>
       <c r="N34">
-        <v>-117.9147968000001</v>
+        <v>-126.6652592</v>
       </c>
       <c r="O34">
-        <v>-19.45594147200001</v>
+        <v>-20.899767768</v>
       </c>
       <c r="P34">
-        <v>-98.45885532800006</v>
+        <v>-105.765491432</v>
       </c>
       <c r="Q34">
-        <v>-51.75885532800004</v>
+        <v>-59.06549143199999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1383156339247804</v>
+        <v>0.1396964642818667</v>
       </c>
       <c r="T34">
-        <v>1.803301904452839</v>
+        <v>1.830216858250643</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.09551816655997514</v>
+        <v>0.09262367666421834</v>
       </c>
       <c r="W34">
-        <v>0.181619952154757</v>
+        <v>0.182201165725825</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5788979791513644</v>
+        <v>0.5613556161467779</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1537230157583729</v>
+        <v>0.1552730157583729</v>
       </c>
       <c r="C35">
-        <v>1046.663505031246</v>
+        <v>968.8094954885789</v>
       </c>
       <c r="D35">
-        <v>2420.837505031246</v>
+        <v>2386.561495488579</v>
       </c>
       <c r="E35">
-        <v>-688.326</v>
+        <v>-644.7479999999998</v>
       </c>
       <c r="F35">
-        <v>1438.074</v>
+        <v>1481.652</v>
       </c>
       <c r="G35">
         <v>63.9</v>
@@ -4291,37 +4291,37 @@
         <v>162.1</v>
       </c>
       <c r="M35">
-        <v>288.7652592</v>
+        <v>297.5157216000001</v>
       </c>
       <c r="N35">
-        <v>-126.6652592</v>
+        <v>-135.4157216000001</v>
       </c>
       <c r="O35">
-        <v>-20.899767768</v>
+        <v>-22.34359406400001</v>
       </c>
       <c r="P35">
-        <v>-105.765491432</v>
+        <v>-113.0721275360001</v>
       </c>
       <c r="Q35">
-        <v>-59.06549143199999</v>
+        <v>-66.37212753600004</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1396964642818667</v>
+        <v>0.1411191379831071</v>
       </c>
       <c r="T35">
-        <v>1.830216858250643</v>
+        <v>1.857947416708986</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.09262367666421834</v>
+        <v>0.0898994508799766</v>
       </c>
       <c r="W35">
-        <v>0.182201165725825</v>
+        <v>0.1827481902633007</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5613556161467779</v>
+        <v>0.544845156848343</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1552730157583729</v>
+        <v>0.1568230157583729</v>
       </c>
       <c r="C36">
-        <v>968.8094954885789</v>
+        <v>891.9125454245848</v>
       </c>
       <c r="D36">
-        <v>2386.561495488579</v>
+        <v>2353.242545424585</v>
       </c>
       <c r="E36">
-        <v>-644.7479999999998</v>
+        <v>-601.1699999999998</v>
       </c>
       <c r="F36">
-        <v>1481.652</v>
+        <v>1525.23</v>
       </c>
       <c r="G36">
         <v>63.9</v>
@@ -4373,37 +4373,37 @@
         <v>162.1</v>
       </c>
       <c r="M36">
-        <v>297.5157216000001</v>
+        <v>306.2661840000001</v>
       </c>
       <c r="N36">
-        <v>-135.4157216000001</v>
+        <v>-144.1661840000001</v>
       </c>
       <c r="O36">
-        <v>-22.34359406400001</v>
+        <v>-23.78742036000001</v>
       </c>
       <c r="P36">
-        <v>-113.0721275360001</v>
+        <v>-120.3787636400001</v>
       </c>
       <c r="Q36">
-        <v>-66.37212753600004</v>
+        <v>-73.67876364000004</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1411191379831071</v>
+        <v>0.1425855862597703</v>
       </c>
       <c r="T36">
-        <v>1.857947416708986</v>
+        <v>1.886531223119894</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.0898994508799766</v>
+        <v>0.0873308951405487</v>
       </c>
       <c r="W36">
-        <v>0.1827481902633007</v>
+        <v>0.1832639562557778</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.544845156848343</v>
+        <v>0.5292781523669619</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1568230157583729</v>
+        <v>0.1583730157583729</v>
       </c>
       <c r="C37">
-        <v>891.9125454245848</v>
+        <v>815.9331220387419</v>
       </c>
       <c r="D37">
-        <v>2353.242545424585</v>
+        <v>2320.841122038742</v>
       </c>
       <c r="E37">
-        <v>-601.1699999999998</v>
+        <v>-557.5919999999999</v>
       </c>
       <c r="F37">
-        <v>1525.23</v>
+        <v>1568.808</v>
       </c>
       <c r="G37">
         <v>63.9</v>
@@ -4455,37 +4455,37 @@
         <v>162.1</v>
       </c>
       <c r="M37">
-        <v>306.2661840000001</v>
+        <v>315.0166464000001</v>
       </c>
       <c r="N37">
-        <v>-144.1661840000001</v>
+        <v>-152.9166464000001</v>
       </c>
       <c r="O37">
-        <v>-23.78742036000001</v>
+        <v>-25.23124665600001</v>
       </c>
       <c r="P37">
-        <v>-120.3787636400001</v>
+        <v>-127.6853997440001</v>
       </c>
       <c r="Q37">
-        <v>-73.67876364000004</v>
+        <v>-80.98539974400005</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1425855862597703</v>
+        <v>0.1440978610450792</v>
       </c>
       <c r="T37">
-        <v>1.886531223119894</v>
+        <v>1.916008273481142</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.0873308951405487</v>
+        <v>0.08490503694220013</v>
       </c>
       <c r="W37">
-        <v>0.1832639562557778</v>
+        <v>0.1837510685820062</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5292781523669619</v>
+        <v>0.5145759814678795</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1583730157583729</v>
+        <v>0.1599230157583729</v>
       </c>
       <c r="C38">
-        <v>815.9331220387421</v>
+        <v>740.8338402424706</v>
       </c>
       <c r="D38">
-        <v>2320.841122038742</v>
+        <v>2289.31984024247</v>
       </c>
       <c r="E38">
-        <v>-557.5920000000001</v>
+        <v>-514.0140000000001</v>
       </c>
       <c r="F38">
-        <v>1568.808</v>
+        <v>1612.386</v>
       </c>
       <c r="G38">
         <v>63.9</v>
@@ -4537,37 +4537,37 @@
         <v>162.1</v>
       </c>
       <c r="M38">
-        <v>315.0166464</v>
+        <v>323.7671088</v>
       </c>
       <c r="N38">
-        <v>-152.9166464</v>
+        <v>-161.6671088</v>
       </c>
       <c r="O38">
-        <v>-25.231246656</v>
+        <v>-26.675072952</v>
       </c>
       <c r="P38">
-        <v>-127.685399744</v>
+        <v>-134.992035848</v>
       </c>
       <c r="Q38">
-        <v>-80.98539974400001</v>
+        <v>-88.29203584800001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1440978610450792</v>
+        <v>0.1456581445537312</v>
       </c>
       <c r="T38">
-        <v>1.916008273481142</v>
+        <v>1.946421103218938</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08490503694220014</v>
+        <v>0.08261030621403256</v>
       </c>
       <c r="W38">
-        <v>0.1837510685820062</v>
+        <v>0.1842118505122223</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5145759814678796</v>
+        <v>0.5006685225092883</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1599230157583729</v>
+        <v>0.1750674348106977</v>
       </c>
       <c r="C39">
-        <v>740.8338402424706</v>
+        <v>429.048932166934</v>
       </c>
       <c r="D39">
-        <v>2289.31984024247</v>
+        <v>2021.112932166934</v>
       </c>
       <c r="E39">
-        <v>-514.0140000000001</v>
+        <v>-470.4359999999999</v>
       </c>
       <c r="F39">
-        <v>1612.386</v>
+        <v>1655.964</v>
       </c>
       <c r="G39">
         <v>63.9</v>
@@ -4619,45 +4619,45 @@
         <v>162.1</v>
       </c>
       <c r="M39">
-        <v>323.7671088</v>
+        <v>390.4763112000001</v>
       </c>
       <c r="N39">
-        <v>-161.6671088</v>
+        <v>-228.3763112000001</v>
       </c>
       <c r="O39">
-        <v>-26.675072952</v>
+        <v>-37.68209134800001</v>
       </c>
       <c r="P39">
-        <v>-134.992035848</v>
+        <v>-190.6942198520001</v>
       </c>
       <c r="Q39">
-        <v>-88.29203584800001</v>
+        <v>-143.994219852</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1456581445537312</v>
+        <v>0.1477436292277024</v>
       </c>
       <c r="T39">
-        <v>1.946421103218938</v>
+        <v>1.987071081225218</v>
       </c>
       <c r="U39">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.08261030621403256</v>
+        <v>0.06849711296903892</v>
       </c>
       <c r="W39">
-        <v>0.1842118505122223</v>
+        <v>0.2196483807619006</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.5006685225092883</v>
+        <v>0.4151340179941753</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1750674348106977</v>
+        <v>0.1769674348106977</v>
       </c>
       <c r="C40">
-        <v>429.048932166934</v>
+        <v>356.1944995168681</v>
       </c>
       <c r="D40">
-        <v>2021.112932166934</v>
+        <v>1991.836499516868</v>
       </c>
       <c r="E40">
-        <v>-470.4359999999999</v>
+        <v>-426.8579999999999</v>
       </c>
       <c r="F40">
-        <v>1655.964</v>
+        <v>1699.542</v>
       </c>
       <c r="G40">
         <v>63.9</v>
@@ -4701,37 +4701,37 @@
         <v>162.1</v>
       </c>
       <c r="M40">
-        <v>390.4763112000001</v>
+        <v>400.7520036</v>
       </c>
       <c r="N40">
-        <v>-228.3763112000001</v>
+        <v>-238.6520036</v>
       </c>
       <c r="O40">
-        <v>-37.68209134800001</v>
+        <v>-39.37758059400001</v>
       </c>
       <c r="P40">
-        <v>-190.6942198520001</v>
+        <v>-199.274423006</v>
       </c>
       <c r="Q40">
-        <v>-143.994219852</v>
+        <v>-152.574423006</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1477436292277024</v>
+        <v>0.1494148362642221</v>
       </c>
       <c r="T40">
-        <v>1.987071081225218</v>
+        <v>2.019646016983009</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06849711296903892</v>
+        <v>0.06674077673906356</v>
       </c>
       <c r="W40">
-        <v>0.2196483807619006</v>
+        <v>0.2200625248449288</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4151340179941753</v>
+        <v>0.4044895559943247</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1769674348106977</v>
+        <v>0.1788674348106977</v>
       </c>
       <c r="C41">
-        <v>356.1944995168681</v>
+        <v>284.1761124720156</v>
       </c>
       <c r="D41">
-        <v>1991.836499516868</v>
+        <v>1963.396112472016</v>
       </c>
       <c r="E41">
-        <v>-426.8579999999999</v>
+        <v>-383.28</v>
       </c>
       <c r="F41">
-        <v>1699.542</v>
+        <v>1743.12</v>
       </c>
       <c r="G41">
         <v>63.9</v>
@@ -4783,37 +4783,37 @@
         <v>162.1</v>
       </c>
       <c r="M41">
-        <v>400.7520036</v>
+        <v>411.027696</v>
       </c>
       <c r="N41">
-        <v>-238.6520036</v>
+        <v>-248.9276960000001</v>
       </c>
       <c r="O41">
-        <v>-39.37758059400001</v>
+        <v>-41.07306984000001</v>
       </c>
       <c r="P41">
-        <v>-199.274423006</v>
+        <v>-207.85462616</v>
       </c>
       <c r="Q41">
-        <v>-152.574423006</v>
+        <v>-161.15462616</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1494148362642221</v>
+        <v>0.1511417502019591</v>
       </c>
       <c r="T41">
-        <v>2.019646016983009</v>
+        <v>2.053306783932726</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06674077673906356</v>
+        <v>0.06507225732058697</v>
       </c>
       <c r="W41">
-        <v>0.2200625248449288</v>
+        <v>0.2204559617238056</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4044895559943247</v>
+        <v>0.3943773170944664</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1788674348106977</v>
+        <v>0.1807674348106977</v>
       </c>
       <c r="C42">
-        <v>284.1761124720156</v>
+        <v>212.9584628118646</v>
       </c>
       <c r="D42">
-        <v>1963.396112472016</v>
+        <v>1935.756462811865</v>
       </c>
       <c r="E42">
-        <v>-383.28</v>
+        <v>-339.7019999999998</v>
       </c>
       <c r="F42">
-        <v>1743.12</v>
+        <v>1786.698</v>
       </c>
       <c r="G42">
         <v>63.9</v>
@@ -4865,37 +4865,37 @@
         <v>162.1</v>
       </c>
       <c r="M42">
-        <v>411.027696</v>
+        <v>421.3033884000001</v>
       </c>
       <c r="N42">
-        <v>-248.9276960000001</v>
+        <v>-259.2033884000001</v>
       </c>
       <c r="O42">
-        <v>-41.07306984000001</v>
+        <v>-42.76855908600002</v>
       </c>
       <c r="P42">
-        <v>-207.85462616</v>
+        <v>-216.4348293140001</v>
       </c>
       <c r="Q42">
-        <v>-161.15462616</v>
+        <v>-169.7348293140001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1511417502019591</v>
+        <v>0.1529272035952127</v>
       </c>
       <c r="T42">
-        <v>2.053306783932726</v>
+        <v>2.088108593829891</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06507225732058697</v>
+        <v>0.06348512909325559</v>
       </c>
       <c r="W42">
-        <v>0.2204559617238056</v>
+        <v>0.2208302065598103</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3943773170944664</v>
+        <v>0.3847583581409428</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1807674348106977</v>
+        <v>0.1826674348106977</v>
       </c>
       <c r="C43">
-        <v>212.9584628118646</v>
+        <v>142.5082029172486</v>
       </c>
       <c r="D43">
-        <v>1935.756462811865</v>
+        <v>1908.884202917249</v>
       </c>
       <c r="E43">
-        <v>-339.7019999999998</v>
+        <v>-296.1239999999998</v>
       </c>
       <c r="F43">
-        <v>1786.698</v>
+        <v>1830.276</v>
       </c>
       <c r="G43">
         <v>63.9</v>
@@ -4947,37 +4947,37 @@
         <v>162.1</v>
       </c>
       <c r="M43">
-        <v>421.3033884000001</v>
+        <v>431.5790808000001</v>
       </c>
       <c r="N43">
-        <v>-259.2033884000001</v>
+        <v>-269.4790808000001</v>
       </c>
       <c r="O43">
-        <v>-42.76855908600002</v>
+        <v>-44.46404833200003</v>
       </c>
       <c r="P43">
-        <v>-216.4348293140001</v>
+        <v>-225.0150324680001</v>
       </c>
       <c r="Q43">
-        <v>-169.7348293140001</v>
+        <v>-178.3150324680001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1529272035952127</v>
+        <v>0.1547742243468543</v>
       </c>
       <c r="T43">
-        <v>2.088108593829891</v>
+        <v>2.124110466137302</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06348512909325559</v>
+        <v>0.06197357840055902</v>
       </c>
       <c r="W43">
-        <v>0.2208302065598103</v>
+        <v>0.2211866302131482</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3847583581409428</v>
+        <v>0.3755974448518727</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1826674348106977</v>
+        <v>0.1845674348106977</v>
       </c>
       <c r="C44">
-        <v>142.5082029172488</v>
+        <v>72.79381154782914</v>
       </c>
       <c r="D44">
-        <v>1908.884202917249</v>
+        <v>1882.747811547829</v>
       </c>
       <c r="E44">
-        <v>-296.124</v>
+        <v>-252.546</v>
       </c>
       <c r="F44">
-        <v>1830.276</v>
+        <v>1873.854</v>
       </c>
       <c r="G44">
         <v>63.9</v>
@@ -5029,37 +5029,37 @@
         <v>162.1</v>
       </c>
       <c r="M44">
-        <v>431.5790808</v>
+        <v>441.8547732</v>
       </c>
       <c r="N44">
-        <v>-269.4790808</v>
+        <v>-279.7547732</v>
       </c>
       <c r="O44">
-        <v>-44.464048332</v>
+        <v>-46.15953757800001</v>
       </c>
       <c r="P44">
-        <v>-225.015032468</v>
+        <v>-233.595235622</v>
       </c>
       <c r="Q44">
-        <v>-178.315032468</v>
+        <v>-186.895235622</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1547742243468543</v>
+        <v>0.1566860528441675</v>
       </c>
       <c r="T44">
-        <v>2.124110466137302</v>
+        <v>2.161375562034448</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06197357840055902</v>
+        <v>0.06053233239124371</v>
       </c>
       <c r="W44">
-        <v>0.2211866302131482</v>
+        <v>0.2215264760221448</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.375597444851873</v>
+        <v>0.366862620552992</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1845674348106977</v>
+        <v>0.1864674348106977</v>
       </c>
       <c r="C45">
-        <v>72.79381154782914</v>
+        <v>3.785470497287861</v>
       </c>
       <c r="D45">
-        <v>1882.747811547829</v>
+        <v>1857.317470497288</v>
       </c>
       <c r="E45">
-        <v>-252.546</v>
+        <v>-208.9680000000001</v>
       </c>
       <c r="F45">
-        <v>1873.854</v>
+        <v>1917.432</v>
       </c>
       <c r="G45">
         <v>63.9</v>
@@ -5111,37 +5111,37 @@
         <v>162.1</v>
       </c>
       <c r="M45">
-        <v>441.8547732</v>
+        <v>452.1304656</v>
       </c>
       <c r="N45">
-        <v>-279.7547732</v>
+        <v>-290.0304656000001</v>
       </c>
       <c r="O45">
-        <v>-46.15953757800001</v>
+        <v>-47.85502682400001</v>
       </c>
       <c r="P45">
-        <v>-233.595235622</v>
+        <v>-242.175438776</v>
       </c>
       <c r="Q45">
-        <v>-186.895235622</v>
+        <v>-195.475438776</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1566860528441675</v>
+        <v>0.1586661609306705</v>
       </c>
       <c r="T45">
-        <v>2.161375562034448</v>
+        <v>2.199971554213635</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06053233239124371</v>
+        <v>0.05915659756416997</v>
       </c>
       <c r="W45">
-        <v>0.2215264760221448</v>
+        <v>0.2218508742943687</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.366862620552992</v>
+        <v>0.3585248337222422</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1864674348106977</v>
+        <v>0.1883674348106977</v>
       </c>
       <c r="C46">
-        <v>3.785470497287861</v>
+        <v>-64.54504888857764</v>
       </c>
       <c r="D46">
-        <v>1857.317470497288</v>
+        <v>1832.564951111422</v>
       </c>
       <c r="E46">
-        <v>-208.9680000000001</v>
+        <v>-165.3899999999999</v>
       </c>
       <c r="F46">
-        <v>1917.432</v>
+        <v>1961.01</v>
       </c>
       <c r="G46">
         <v>63.9</v>
@@ -5193,37 +5193,37 @@
         <v>162.1</v>
       </c>
       <c r="M46">
-        <v>452.1304656</v>
+        <v>462.4061580000001</v>
       </c>
       <c r="N46">
-        <v>-290.0304656000001</v>
+        <v>-300.3061580000001</v>
       </c>
       <c r="O46">
-        <v>-47.85502682400001</v>
+        <v>-49.55051607000001</v>
       </c>
       <c r="P46">
-        <v>-242.175438776</v>
+        <v>-250.7556419300001</v>
       </c>
       <c r="Q46">
-        <v>-195.475438776</v>
+        <v>-204.0556419300001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1586661609306705</v>
+        <v>0.1607182729475918</v>
       </c>
       <c r="T46">
-        <v>2.199971554213635</v>
+        <v>2.239971037017519</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05915659756416997</v>
+        <v>0.05784200650718842</v>
       </c>
       <c r="W46">
-        <v>0.2218508742943687</v>
+        <v>0.222160854865605</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3585248337222422</v>
+        <v>0.3505576151950812</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1883674348106977</v>
+        <v>0.1902674348106977</v>
       </c>
       <c r="C47">
-        <v>-64.54504888857764</v>
+        <v>-132.224490238832</v>
       </c>
       <c r="D47">
-        <v>1832.564951111422</v>
+        <v>1808.463509761168</v>
       </c>
       <c r="E47">
-        <v>-165.3899999999999</v>
+        <v>-121.8119999999999</v>
       </c>
       <c r="F47">
-        <v>1961.01</v>
+        <v>2004.588</v>
       </c>
       <c r="G47">
         <v>63.9</v>
@@ -5275,37 +5275,37 @@
         <v>162.1</v>
       </c>
       <c r="M47">
-        <v>462.4061580000001</v>
+        <v>472.6818504000001</v>
       </c>
       <c r="N47">
-        <v>-300.3061580000001</v>
+        <v>-310.5818504000001</v>
       </c>
       <c r="O47">
-        <v>-49.55051607000001</v>
+        <v>-51.24600531600002</v>
       </c>
       <c r="P47">
-        <v>-250.7556419300001</v>
+        <v>-259.3358450840001</v>
       </c>
       <c r="Q47">
-        <v>-204.0556419300001</v>
+        <v>-212.6358450840001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1607182729475918</v>
+        <v>0.1628463891132879</v>
       </c>
       <c r="T47">
-        <v>2.239971037017519</v>
+        <v>2.281451982147473</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05784200650718842</v>
+        <v>0.0565845715831191</v>
       </c>
       <c r="W47">
-        <v>0.222160854865605</v>
+        <v>0.2224573580207005</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3505576151950812</v>
+        <v>0.3429367974734491</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1902674348106977</v>
+        <v>0.1921674348106978</v>
       </c>
       <c r="C48">
-        <v>-132.224490238832</v>
+        <v>-199.2782085431818</v>
       </c>
       <c r="D48">
-        <v>1808.463509761168</v>
+        <v>1784.987791456818</v>
       </c>
       <c r="E48">
-        <v>-121.8119999999999</v>
+        <v>-78.23399999999992</v>
       </c>
       <c r="F48">
-        <v>2004.588</v>
+        <v>2048.166</v>
       </c>
       <c r="G48">
         <v>63.9</v>
@@ -5357,37 +5357,37 @@
         <v>162.1</v>
       </c>
       <c r="M48">
-        <v>472.6818504000001</v>
+        <v>482.9575428000001</v>
       </c>
       <c r="N48">
-        <v>-310.5818504000001</v>
+        <v>-320.8575428</v>
       </c>
       <c r="O48">
-        <v>-51.24600531600002</v>
+        <v>-52.94149456200001</v>
       </c>
       <c r="P48">
-        <v>-259.3358450840001</v>
+        <v>-267.916048238</v>
       </c>
       <c r="Q48">
-        <v>-212.6358450840001</v>
+        <v>-221.216048238</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1628463891132879</v>
+        <v>0.1650548115493877</v>
       </c>
       <c r="T48">
-        <v>2.281451982147473</v>
+        <v>2.324498245961577</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0565845715831191</v>
+        <v>0.05538064452815913</v>
       </c>
       <c r="W48">
-        <v>0.2224573580207005</v>
+        <v>0.2227412440202601</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3429367974734491</v>
+        <v>0.3356402698676311</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1921674348106978</v>
+        <v>0.1940674348106977</v>
       </c>
       <c r="C49">
-        <v>-199.2782085431818</v>
+        <v>-265.7302591268315</v>
       </c>
       <c r="D49">
-        <v>1784.987791456818</v>
+        <v>1762.113740873169</v>
       </c>
       <c r="E49">
-        <v>-78.23399999999992</v>
+        <v>-34.65599999999995</v>
       </c>
       <c r="F49">
-        <v>2048.166</v>
+        <v>2091.744</v>
       </c>
       <c r="G49">
         <v>63.9</v>
@@ -5439,37 +5439,37 @@
         <v>162.1</v>
       </c>
       <c r="M49">
-        <v>482.9575428000001</v>
+        <v>493.2332352000001</v>
       </c>
       <c r="N49">
-        <v>-320.8575428</v>
+        <v>-331.1332352000001</v>
       </c>
       <c r="O49">
-        <v>-52.94149456200001</v>
+        <v>-54.63698380800001</v>
       </c>
       <c r="P49">
-        <v>-267.916048238</v>
+        <v>-276.496251392</v>
       </c>
       <c r="Q49">
-        <v>-221.216048238</v>
+        <v>-229.796251392</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1650548115493877</v>
+        <v>0.1673481733099528</v>
       </c>
       <c r="T49">
-        <v>2.324498245961577</v>
+        <v>2.369200135306991</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05538064452815913</v>
+        <v>0.05422688110048914</v>
       </c>
       <c r="W49">
-        <v>0.2227412440202601</v>
+        <v>0.2230133014365047</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3356402698676311</v>
+        <v>0.3286477642453888</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1940674348106977</v>
+        <v>0.1959674348106977</v>
       </c>
       <c r="C50">
-        <v>-265.7302591268315</v>
+        <v>-331.6034798707935</v>
       </c>
       <c r="D50">
-        <v>1762.113740873169</v>
+        <v>1739.818520129206</v>
       </c>
       <c r="E50">
-        <v>-34.65599999999995</v>
+        <v>8.922000000000025</v>
       </c>
       <c r="F50">
-        <v>2091.744</v>
+        <v>2135.322</v>
       </c>
       <c r="G50">
         <v>63.9</v>
@@ -5521,37 +5521,37 @@
         <v>162.1</v>
       </c>
       <c r="M50">
-        <v>493.2332352000001</v>
+        <v>503.5089276</v>
       </c>
       <c r="N50">
-        <v>-331.1332352000001</v>
+        <v>-341.4089276000001</v>
       </c>
       <c r="O50">
-        <v>-54.63698380800001</v>
+        <v>-56.33247305400002</v>
       </c>
       <c r="P50">
-        <v>-276.496251392</v>
+        <v>-285.076454546</v>
       </c>
       <c r="Q50">
-        <v>-229.796251392</v>
+        <v>-238.376454546</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1673481733099528</v>
+        <v>0.1697314708258343</v>
       </c>
       <c r="T50">
-        <v>2.369200135306991</v>
+        <v>2.415655039920854</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05422688110048914</v>
+        <v>0.05312021005762202</v>
       </c>
       <c r="W50">
-        <v>0.2230133014365047</v>
+        <v>0.2232742544684127</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3286477642453888</v>
+        <v>0.321940667015891</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1959674348106977</v>
+        <v>0.1978674348106977</v>
       </c>
       <c r="C51">
-        <v>-331.6034798707935</v>
+        <v>-396.9195672684048</v>
       </c>
       <c r="D51">
-        <v>1739.818520129206</v>
+        <v>1718.080432731595</v>
       </c>
       <c r="E51">
-        <v>8.922000000000025</v>
+        <v>52.5</v>
       </c>
       <c r="F51">
-        <v>2135.322</v>
+        <v>2178.9</v>
       </c>
       <c r="G51">
         <v>63.9</v>
@@ -5603,37 +5603,37 @@
         <v>162.1</v>
       </c>
       <c r="M51">
-        <v>503.5089276</v>
+        <v>513.78462</v>
       </c>
       <c r="N51">
-        <v>-341.4089276000001</v>
+        <v>-351.68462</v>
       </c>
       <c r="O51">
-        <v>-56.33247305400002</v>
+        <v>-58.0279623</v>
       </c>
       <c r="P51">
-        <v>-285.076454546</v>
+        <v>-293.6566577</v>
       </c>
       <c r="Q51">
-        <v>-238.376454546</v>
+        <v>-246.9566577</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1697314708258343</v>
+        <v>0.172210100242351</v>
       </c>
       <c r="T51">
-        <v>2.415655039920854</v>
+        <v>2.463968140719271</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05312021005762202</v>
+        <v>0.05205780585646958</v>
       </c>
       <c r="W51">
-        <v>0.2232742544684127</v>
+        <v>0.2235247693790445</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.321940667015891</v>
+        <v>0.3155018536755733</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1978674348106977</v>
+        <v>0.1997674348106978</v>
       </c>
       <c r="C52">
-        <v>-396.9195672684048</v>
+        <v>-461.6991468505</v>
       </c>
       <c r="D52">
-        <v>1718.080432731595</v>
+        <v>1696.8788531495</v>
       </c>
       <c r="E52">
-        <v>52.5</v>
+        <v>96.07799999999997</v>
       </c>
       <c r="F52">
-        <v>2178.9</v>
+        <v>2222.478</v>
       </c>
       <c r="G52">
         <v>63.9</v>
@@ -5685,37 +5685,37 @@
         <v>162.1</v>
       </c>
       <c r="M52">
-        <v>513.78462</v>
+        <v>524.0603124</v>
       </c>
       <c r="N52">
-        <v>-351.68462</v>
+        <v>-361.9603124</v>
       </c>
       <c r="O52">
-        <v>-58.0279623</v>
+        <v>-59.72345154600001</v>
       </c>
       <c r="P52">
-        <v>-293.6566577</v>
+        <v>-302.236860854</v>
       </c>
       <c r="Q52">
-        <v>-246.9566577</v>
+        <v>-255.536860854</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.172210100242351</v>
+        <v>0.1747898982064806</v>
       </c>
       <c r="T52">
-        <v>2.463968140719271</v>
+        <v>2.514253204815583</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05205780585646958</v>
+        <v>0.05103706456516626</v>
       </c>
       <c r="W52">
-        <v>0.2235247693790445</v>
+        <v>0.2237654601755338</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3155018536755733</v>
+        <v>0.3093155428191895</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1997674348106978</v>
+        <v>0.2016674348106978</v>
       </c>
       <c r="C53">
-        <v>-461.6991468505</v>
+        <v>-525.9618384597495</v>
       </c>
       <c r="D53">
-        <v>1696.8788531495</v>
+        <v>1676.19416154025</v>
       </c>
       <c r="E53">
-        <v>96.07799999999997</v>
+        <v>139.6559999999999</v>
       </c>
       <c r="F53">
-        <v>2222.478</v>
+        <v>2266.056</v>
       </c>
       <c r="G53">
         <v>63.9</v>
@@ -5767,37 +5767,37 @@
         <v>162.1</v>
       </c>
       <c r="M53">
-        <v>524.0603124</v>
+        <v>534.3360048000001</v>
       </c>
       <c r="N53">
-        <v>-361.9603124</v>
+        <v>-372.2360048</v>
       </c>
       <c r="O53">
-        <v>-59.72345154600001</v>
+        <v>-61.41894079200001</v>
       </c>
       <c r="P53">
-        <v>-302.236860854</v>
+        <v>-310.817064008</v>
       </c>
       <c r="Q53">
-        <v>-255.536860854</v>
+        <v>-264.1170640080001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1747898982064806</v>
+        <v>0.177477187752449</v>
       </c>
       <c r="T53">
-        <v>2.514253204815583</v>
+        <v>2.566633479915908</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05103706456516626</v>
+        <v>0.05005558255429767</v>
       </c>
       <c r="W53">
-        <v>0.2237654601755338</v>
+        <v>0.2239968936336966</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3093155428191895</v>
+        <v>0.3033671669957435</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2016674348106978</v>
+        <v>0.2035674348106977</v>
       </c>
       <c r="C54">
-        <v>-525.9618384597495</v>
+        <v>-589.7263168083878</v>
       </c>
       <c r="D54">
-        <v>1676.19416154025</v>
+        <v>1656.007683191612</v>
       </c>
       <c r="E54">
-        <v>139.6559999999999</v>
+        <v>183.2339999999999</v>
       </c>
       <c r="F54">
-        <v>2266.056</v>
+        <v>2309.634</v>
       </c>
       <c r="G54">
         <v>63.9</v>
@@ -5849,37 +5849,37 @@
         <v>162.1</v>
       </c>
       <c r="M54">
-        <v>534.3360048000001</v>
+        <v>544.6116972</v>
       </c>
       <c r="N54">
-        <v>-372.2360048</v>
+        <v>-382.5116972</v>
       </c>
       <c r="O54">
-        <v>-61.41894079200001</v>
+        <v>-63.11443003799999</v>
       </c>
       <c r="P54">
-        <v>-310.817064008</v>
+        <v>-319.3972671619999</v>
       </c>
       <c r="Q54">
-        <v>-264.1170640080001</v>
+        <v>-272.6972671619999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.177477187752449</v>
+        <v>0.1802788300450542</v>
       </c>
       <c r="T54">
-        <v>2.566633479915908</v>
+        <v>2.621242702892841</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05005558255429767</v>
+        <v>0.04911113760044301</v>
       </c>
       <c r="W54">
-        <v>0.2239968936336966</v>
+        <v>0.2242195937538155</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3033671669957435</v>
+        <v>0.2976432581845031</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2035674348106977</v>
+        <v>0.2054674348106977</v>
       </c>
       <c r="C55">
-        <v>-589.7263168083878</v>
+        <v>-653.0103677122218</v>
       </c>
       <c r="D55">
-        <v>1656.007683191612</v>
+        <v>1636.301632287779</v>
       </c>
       <c r="E55">
-        <v>183.2339999999999</v>
+        <v>226.8120000000004</v>
       </c>
       <c r="F55">
-        <v>2309.634</v>
+        <v>2353.212</v>
       </c>
       <c r="G55">
         <v>63.9</v>
@@ -5931,37 +5931,37 @@
         <v>162.1</v>
       </c>
       <c r="M55">
-        <v>544.6116972</v>
+        <v>554.8873896000001</v>
       </c>
       <c r="N55">
-        <v>-382.5116972</v>
+        <v>-392.7873896000001</v>
       </c>
       <c r="O55">
-        <v>-63.11443003799999</v>
+        <v>-64.80991928400002</v>
       </c>
       <c r="P55">
-        <v>-319.3972671619999</v>
+        <v>-327.9774703160001</v>
       </c>
       <c r="Q55">
-        <v>-272.6972671619999</v>
+        <v>-281.2774703160001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1802788300450542</v>
+        <v>0.1832022828721206</v>
       </c>
       <c r="T55">
-        <v>2.621242702892841</v>
+        <v>2.678226239912251</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04911113760044301</v>
+        <v>0.04820167208932368</v>
       </c>
       <c r="W55">
-        <v>0.2242195937538155</v>
+        <v>0.2244340457213375</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2976432581845031</v>
+        <v>0.2921313459959011</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2054674348106977</v>
+        <v>0.2073674348106977</v>
       </c>
       <c r="C56">
-        <v>-653.0103677122218</v>
+        <v>-715.8309403568228</v>
       </c>
       <c r="D56">
-        <v>1636.301632287779</v>
+        <v>1617.059059643178</v>
       </c>
       <c r="E56">
-        <v>226.8120000000004</v>
+        <v>270.3900000000003</v>
       </c>
       <c r="F56">
-        <v>2353.212</v>
+        <v>2396.79</v>
       </c>
       <c r="G56">
         <v>63.9</v>
@@ -6013,37 +6013,37 @@
         <v>162.1</v>
       </c>
       <c r="M56">
-        <v>554.8873896000001</v>
+        <v>565.1630820000001</v>
       </c>
       <c r="N56">
-        <v>-392.7873896000001</v>
+        <v>-403.0630820000001</v>
       </c>
       <c r="O56">
-        <v>-64.80991928400002</v>
+        <v>-66.50540853000003</v>
       </c>
       <c r="P56">
-        <v>-327.9774703160001</v>
+        <v>-336.5576734700001</v>
       </c>
       <c r="Q56">
-        <v>-281.2774703160001</v>
+        <v>-289.8576734700001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1832022828721206</v>
+        <v>0.1862556669359455</v>
       </c>
       <c r="T56">
-        <v>2.678226239912251</v>
+        <v>2.737742378576968</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04820167208932368</v>
+        <v>0.04732527805133598</v>
       </c>
       <c r="W56">
-        <v>0.2244340457213375</v>
+        <v>0.224640699435495</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2921313459959011</v>
+        <v>0.2868198669777938</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2073674348106977</v>
+        <v>0.2092674348106978</v>
       </c>
       <c r="C57">
-        <v>-715.8309403568228</v>
+        <v>-778.2041959187648</v>
       </c>
       <c r="D57">
-        <v>1617.059059643178</v>
+        <v>1598.263804081236</v>
       </c>
       <c r="E57">
-        <v>270.3900000000003</v>
+        <v>313.9680000000003</v>
       </c>
       <c r="F57">
-        <v>2396.79</v>
+        <v>2440.368</v>
       </c>
       <c r="G57">
         <v>63.9</v>
@@ -6095,37 +6095,37 @@
         <v>162.1</v>
       </c>
       <c r="M57">
-        <v>565.1630820000001</v>
+        <v>575.4387744000002</v>
       </c>
       <c r="N57">
-        <v>-403.0630820000001</v>
+        <v>-413.3387744000001</v>
       </c>
       <c r="O57">
-        <v>-66.50540853000003</v>
+        <v>-68.20089777600003</v>
       </c>
       <c r="P57">
-        <v>-336.5576734700001</v>
+        <v>-345.1378766240001</v>
       </c>
       <c r="Q57">
-        <v>-289.8576734700001</v>
+        <v>-298.4378766240001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1862556669359455</v>
+        <v>0.1894478411844898</v>
       </c>
       <c r="T57">
-        <v>2.737742378576968</v>
+        <v>2.799963796271899</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04732527805133598</v>
+        <v>0.04648018380041926</v>
       </c>
       <c r="W57">
-        <v>0.224640699435495</v>
+        <v>0.2248399726598611</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2868198669777938</v>
+        <v>0.2816980836389046</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2092674348106978</v>
+        <v>0.2111674348106977</v>
       </c>
       <c r="C58">
-        <v>-778.2041959187648</v>
+        <v>-840.1455528350191</v>
       </c>
       <c r="D58">
-        <v>1598.263804081236</v>
+        <v>1579.900447164981</v>
       </c>
       <c r="E58">
-        <v>313.9680000000003</v>
+        <v>357.5460000000003</v>
       </c>
       <c r="F58">
-        <v>2440.368</v>
+        <v>2483.946</v>
       </c>
       <c r="G58">
         <v>63.9</v>
@@ -6177,37 +6177,37 @@
         <v>162.1</v>
       </c>
       <c r="M58">
-        <v>575.4387744000002</v>
+        <v>585.7144668000001</v>
       </c>
       <c r="N58">
-        <v>-413.3387744000001</v>
+        <v>-423.6144668000001</v>
       </c>
       <c r="O58">
-        <v>-68.20089777600003</v>
+        <v>-69.89638702200001</v>
       </c>
       <c r="P58">
-        <v>-345.1378766240001</v>
+        <v>-353.7180797780001</v>
       </c>
       <c r="Q58">
-        <v>-298.4378766240001</v>
+        <v>-307.018079778</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1894478411844898</v>
+        <v>0.1927884886538965</v>
       </c>
       <c r="T58">
-        <v>2.799963796271899</v>
+        <v>2.865079233394502</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04648018380041926</v>
+        <v>0.04566474197935928</v>
       </c>
       <c r="W58">
-        <v>0.2248399726598611</v>
+        <v>0.2250322538412671</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2816980836389046</v>
+        <v>0.2767560119961169</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2111674348106977</v>
+        <v>0.2130674348106977</v>
       </c>
       <c r="C59">
-        <v>-840.1455528350191</v>
+        <v>-901.6697289870638</v>
       </c>
       <c r="D59">
-        <v>1579.900447164981</v>
+        <v>1561.954271012936</v>
       </c>
       <c r="E59">
-        <v>357.5460000000003</v>
+        <v>401.1240000000003</v>
       </c>
       <c r="F59">
-        <v>2483.946</v>
+        <v>2527.524</v>
       </c>
       <c r="G59">
         <v>63.9</v>
@@ -6259,37 +6259,37 @@
         <v>162.1</v>
       </c>
       <c r="M59">
-        <v>585.7144668000001</v>
+        <v>595.9901592000001</v>
       </c>
       <c r="N59">
-        <v>-423.6144668000001</v>
+        <v>-433.8901592000001</v>
       </c>
       <c r="O59">
-        <v>-69.89638702200001</v>
+        <v>-71.59187626800002</v>
       </c>
       <c r="P59">
-        <v>-353.7180797780001</v>
+        <v>-362.2982829320001</v>
       </c>
       <c r="Q59">
-        <v>-307.018079778</v>
+        <v>-315.5982829320001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1927884886538965</v>
+        <v>0.1962882145742274</v>
       </c>
       <c r="T59">
-        <v>2.865079233394502</v>
+        <v>2.93329540561818</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04566474197935928</v>
+        <v>0.04487741884178412</v>
       </c>
       <c r="W59">
-        <v>0.2250322538412671</v>
+        <v>0.2252179046371073</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2767560119961169</v>
+        <v>0.2719843566168735</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2130674348106977</v>
+        <v>0.2149674348106977</v>
       </c>
       <c r="C60">
-        <v>-901.6697289870633</v>
+        <v>-962.7907810422389</v>
       </c>
       <c r="D60">
-        <v>1561.954271012936</v>
+        <v>1544.411218957761</v>
       </c>
       <c r="E60">
-        <v>401.1239999999998</v>
+        <v>444.7019999999998</v>
       </c>
       <c r="F60">
-        <v>2527.524</v>
+        <v>2571.102</v>
       </c>
       <c r="G60">
         <v>63.9</v>
@@ -6341,37 +6341,37 @@
         <v>162.1</v>
       </c>
       <c r="M60">
-        <v>595.9901592</v>
+        <v>606.2658516</v>
       </c>
       <c r="N60">
-        <v>-433.8901592</v>
+        <v>-444.1658516</v>
       </c>
       <c r="O60">
-        <v>-71.59187626799999</v>
+        <v>-73.287365514</v>
       </c>
       <c r="P60">
-        <v>-362.298282932</v>
+        <v>-370.878486086</v>
       </c>
       <c r="Q60">
-        <v>-315.598282932</v>
+        <v>-324.178486086</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1962882145742273</v>
+        <v>0.1999586588321353</v>
       </c>
       <c r="T60">
-        <v>2.93329540561818</v>
+        <v>3.004839195999111</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04487741884178412</v>
+        <v>0.04411678462412677</v>
       </c>
       <c r="W60">
-        <v>0.2252179046371073</v>
+        <v>0.2253972621856309</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2719843566168735</v>
+        <v>0.2673744522674349</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2149674348106977</v>
+        <v>0.2168674348106978</v>
       </c>
       <c r="C61">
-        <v>-962.7907810422389</v>
+        <v>-1023.522141173388</v>
       </c>
       <c r="D61">
-        <v>1544.411218957761</v>
+        <v>1527.257858826612</v>
       </c>
       <c r="E61">
-        <v>444.7019999999998</v>
+        <v>488.2799999999997</v>
       </c>
       <c r="F61">
-        <v>2571.102</v>
+        <v>2614.68</v>
       </c>
       <c r="G61">
         <v>63.9</v>
@@ -6423,37 +6423,37 @@
         <v>162.1</v>
       </c>
       <c r="M61">
-        <v>606.2658516</v>
+        <v>616.5415439999999</v>
       </c>
       <c r="N61">
-        <v>-444.1658516</v>
+        <v>-454.4415439999999</v>
       </c>
       <c r="O61">
-        <v>-73.287365514</v>
+        <v>-74.98285476</v>
       </c>
       <c r="P61">
-        <v>-370.878486086</v>
+        <v>-379.4586892399999</v>
       </c>
       <c r="Q61">
-        <v>-324.178486086</v>
+        <v>-332.7586892399999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1999586588321353</v>
+        <v>0.2038126253029387</v>
       </c>
       <c r="T61">
-        <v>3.004839195999111</v>
+        <v>3.079960175899089</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04411678462412677</v>
+        <v>0.04338150488039132</v>
       </c>
       <c r="W61">
-        <v>0.2253972621856309</v>
+        <v>0.2255706411492037</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2673744522674349</v>
+        <v>0.2629182113963111</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2168674348106978</v>
+        <v>0.2187674348106977</v>
       </c>
       <c r="C62">
-        <v>-1023.522141173388</v>
+        <v>-1083.876651358363</v>
       </c>
       <c r="D62">
-        <v>1527.257858826612</v>
+        <v>1510.481348641638</v>
       </c>
       <c r="E62">
-        <v>488.2799999999997</v>
+        <v>531.8580000000002</v>
       </c>
       <c r="F62">
-        <v>2614.68</v>
+        <v>2658.258</v>
       </c>
       <c r="G62">
         <v>63.9</v>
@@ -6505,37 +6505,37 @@
         <v>162.1</v>
       </c>
       <c r="M62">
-        <v>616.5415439999999</v>
+        <v>626.8172364000001</v>
       </c>
       <c r="N62">
-        <v>-454.4415439999999</v>
+        <v>-464.7172364</v>
       </c>
       <c r="O62">
-        <v>-74.98285476</v>
+        <v>-76.67834400600002</v>
       </c>
       <c r="P62">
-        <v>-379.4586892399999</v>
+        <v>-388.038892394</v>
       </c>
       <c r="Q62">
-        <v>-332.7586892399999</v>
+        <v>-341.338892394</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2038126253029387</v>
+        <v>0.2078642310799371</v>
       </c>
       <c r="T62">
-        <v>3.079960175899089</v>
+        <v>3.158933513742655</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04338150488039132</v>
+        <v>0.04267033266923736</v>
       </c>
       <c r="W62">
-        <v>0.2255706411492037</v>
+        <v>0.2257383355565938</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2629182113963111</v>
+        <v>0.2586080767832568</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2187674348106977</v>
+        <v>0.2206674348106977</v>
       </c>
       <c r="C63">
-        <v>-1083.876651358363</v>
+        <v>-1143.866595443469</v>
       </c>
       <c r="D63">
-        <v>1510.481348641638</v>
+        <v>1494.069404556531</v>
       </c>
       <c r="E63">
-        <v>531.8580000000002</v>
+        <v>575.4360000000001</v>
       </c>
       <c r="F63">
-        <v>2658.258</v>
+        <v>2701.836</v>
       </c>
       <c r="G63">
         <v>63.9</v>
@@ -6587,37 +6587,37 @@
         <v>162.1</v>
       </c>
       <c r="M63">
-        <v>626.8172364000001</v>
+        <v>637.0929288000001</v>
       </c>
       <c r="N63">
-        <v>-464.7172364</v>
+        <v>-474.9929288000001</v>
       </c>
       <c r="O63">
-        <v>-76.67834400600002</v>
+        <v>-78.37383325200001</v>
       </c>
       <c r="P63">
-        <v>-388.038892394</v>
+        <v>-396.6190955480001</v>
       </c>
       <c r="Q63">
-        <v>-341.338892394</v>
+        <v>-349.9190955480001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2078642310799371</v>
+        <v>0.2121290792662512</v>
       </c>
       <c r="T63">
-        <v>3.158933513742655</v>
+        <v>3.242063343051672</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04267033266923736</v>
+        <v>0.04198210149715289</v>
       </c>
       <c r="W63">
-        <v>0.2257383355565938</v>
+        <v>0.2259006204669714</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2586080767832568</v>
+        <v>0.2544369787706235</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2206674348106977</v>
+        <v>0.2225674348106977</v>
       </c>
       <c r="C64">
-        <v>-1143.866595443469</v>
+        <v>-1203.503729139092</v>
       </c>
       <c r="D64">
-        <v>1494.069404556531</v>
+        <v>1478.010270860908</v>
       </c>
       <c r="E64">
-        <v>575.4360000000001</v>
+        <v>619.0140000000001</v>
       </c>
       <c r="F64">
-        <v>2701.836</v>
+        <v>2745.414</v>
       </c>
       <c r="G64">
         <v>63.9</v>
@@ -6669,37 +6669,37 @@
         <v>162.1</v>
       </c>
       <c r="M64">
-        <v>637.0929288000001</v>
+        <v>647.3686212000001</v>
       </c>
       <c r="N64">
-        <v>-474.9929288000001</v>
+        <v>-485.2686212000001</v>
       </c>
       <c r="O64">
-        <v>-78.37383325200001</v>
+        <v>-80.06932249800002</v>
       </c>
       <c r="P64">
-        <v>-396.6190955480001</v>
+        <v>-405.1992987020001</v>
       </c>
       <c r="Q64">
-        <v>-349.9190955480001</v>
+        <v>-358.499298702</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2121290792662512</v>
+        <v>0.2166244597869608</v>
       </c>
       <c r="T64">
-        <v>3.242063343051672</v>
+        <v>3.329686676647663</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04198210149715289</v>
+        <v>0.04131571893370602</v>
       </c>
       <c r="W64">
-        <v>0.2259006204669714</v>
+        <v>0.2260577534754321</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2544369787706235</v>
+        <v>0.2503982965679152</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2225674348106977</v>
+        <v>0.2244674348106978</v>
       </c>
       <c r="C65">
-        <v>-1203.503729139092</v>
+        <v>-1262.799308101432</v>
       </c>
       <c r="D65">
-        <v>1478.010270860908</v>
+        <v>1462.292691898569</v>
       </c>
       <c r="E65">
-        <v>619.0140000000001</v>
+        <v>662.5920000000001</v>
       </c>
       <c r="F65">
-        <v>2745.414</v>
+        <v>2788.992</v>
       </c>
       <c r="G65">
         <v>63.9</v>
@@ -6751,37 +6751,37 @@
         <v>162.1</v>
       </c>
       <c r="M65">
-        <v>647.3686212000001</v>
+        <v>657.6443136</v>
       </c>
       <c r="N65">
-        <v>-485.2686212000001</v>
+        <v>-495.5443136</v>
       </c>
       <c r="O65">
-        <v>-80.06932249800002</v>
+        <v>-81.764811744</v>
       </c>
       <c r="P65">
-        <v>-405.1992987020001</v>
+        <v>-413.779501856</v>
       </c>
       <c r="Q65">
-        <v>-358.499298702</v>
+        <v>-367.079501856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2166244597869608</v>
+        <v>0.2213695836699319</v>
       </c>
       <c r="T65">
-        <v>3.329686676647663</v>
+        <v>3.42217797322121</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04131571893370602</v>
+        <v>0.04067016082536686</v>
       </c>
       <c r="W65">
-        <v>0.2260577534754321</v>
+        <v>0.2262099760773785</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2503982965679152</v>
+        <v>0.2464858231840417</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2244674348106978</v>
+        <v>0.2263674348106977</v>
       </c>
       <c r="C66">
-        <v>-1262.799308101432</v>
+        <v>-1321.764114241309</v>
       </c>
       <c r="D66">
-        <v>1462.292691898569</v>
+        <v>1446.905885758691</v>
       </c>
       <c r="E66">
-        <v>662.5920000000001</v>
+        <v>706.1700000000001</v>
       </c>
       <c r="F66">
-        <v>2788.992</v>
+        <v>2832.57</v>
       </c>
       <c r="G66">
         <v>63.9</v>
@@ -6833,37 +6833,37 @@
         <v>162.1</v>
       </c>
       <c r="M66">
-        <v>657.6443136</v>
+        <v>667.9200060000001</v>
       </c>
       <c r="N66">
-        <v>-495.5443136</v>
+        <v>-505.820006</v>
       </c>
       <c r="O66">
-        <v>-81.764811744</v>
+        <v>-83.46030099000001</v>
       </c>
       <c r="P66">
-        <v>-413.779501856</v>
+        <v>-422.35970501</v>
       </c>
       <c r="Q66">
-        <v>-367.079501856</v>
+        <v>-375.65970501</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2213695836699319</v>
+        <v>0.2263858574890728</v>
       </c>
       <c r="T66">
-        <v>3.42217797322121</v>
+        <v>3.519954486741816</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04067016082536686</v>
+        <v>0.04004446604343814</v>
       </c>
       <c r="W66">
-        <v>0.2262099760773785</v>
+        <v>0.2263575149069573</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2464858231840417</v>
+        <v>0.2426937335965949</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2263674348106977</v>
+        <v>0.2282674348106977</v>
       </c>
       <c r="C67">
-        <v>-1321.764114241309</v>
+        <v>-1380.408480389294</v>
       </c>
       <c r="D67">
-        <v>1446.905885758691</v>
+        <v>1431.839519610706</v>
       </c>
       <c r="E67">
-        <v>706.1700000000001</v>
+        <v>749.748</v>
       </c>
       <c r="F67">
-        <v>2832.57</v>
+        <v>2876.148</v>
       </c>
       <c r="G67">
         <v>63.9</v>
@@ -6915,37 +6915,37 @@
         <v>162.1</v>
       </c>
       <c r="M67">
-        <v>667.9200060000001</v>
+        <v>678.1956984000001</v>
       </c>
       <c r="N67">
-        <v>-505.820006</v>
+        <v>-516.0956984000001</v>
       </c>
       <c r="O67">
-        <v>-83.46030099000001</v>
+        <v>-85.15579023600002</v>
       </c>
       <c r="P67">
-        <v>-422.35970501</v>
+        <v>-430.939908164</v>
       </c>
       <c r="Q67">
-        <v>-375.65970501</v>
+        <v>-384.239908164</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2263858574890728</v>
+        <v>0.2316972062387514</v>
       </c>
       <c r="T67">
-        <v>3.519954486741816</v>
+        <v>3.623482559881281</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04004446604343814</v>
+        <v>0.03943773170944665</v>
       </c>
       <c r="W67">
-        <v>0.2263575149069573</v>
+        <v>0.2265005828629125</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2426937335965949</v>
+        <v>0.2390165558148282</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2282674348106977</v>
+        <v>0.2301674348106977</v>
       </c>
       <c r="C68">
-        <v>-1380.408480389294</v>
+        <v>-1438.742313435698</v>
       </c>
       <c r="D68">
-        <v>1431.839519610706</v>
+        <v>1417.083686564302</v>
       </c>
       <c r="E68">
-        <v>749.748</v>
+        <v>793.326</v>
       </c>
       <c r="F68">
-        <v>2876.148</v>
+        <v>2919.726</v>
       </c>
       <c r="G68">
         <v>63.9</v>
@@ -6997,37 +6997,37 @@
         <v>162.1</v>
       </c>
       <c r="M68">
-        <v>678.1956984000001</v>
+        <v>688.4713908000001</v>
       </c>
       <c r="N68">
-        <v>-516.0956984000001</v>
+        <v>-526.3713908000001</v>
       </c>
       <c r="O68">
-        <v>-85.15579023600002</v>
+        <v>-86.85127948200002</v>
       </c>
       <c r="P68">
-        <v>-430.939908164</v>
+        <v>-439.5201113180001</v>
       </c>
       <c r="Q68">
-        <v>-384.239908164</v>
+        <v>-392.820111318</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2316972062387514</v>
+        <v>0.237330454912653</v>
       </c>
       <c r="T68">
-        <v>3.623482559881281</v>
+        <v>3.733285061695866</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03943773170944665</v>
+        <v>0.03884910884811162</v>
       </c>
       <c r="W68">
-        <v>0.2265005828629125</v>
+        <v>0.2266393801336153</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2390165558148282</v>
+        <v>0.2354491445340099</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2301674348106977</v>
+        <v>0.2320674348106977</v>
       </c>
       <c r="C69">
-        <v>-1438.742313435698</v>
+        <v>-1496.775116054355</v>
       </c>
       <c r="D69">
-        <v>1417.083686564302</v>
+        <v>1402.628883945645</v>
       </c>
       <c r="E69">
-        <v>793.326</v>
+        <v>836.9040000000005</v>
       </c>
       <c r="F69">
-        <v>2919.726</v>
+        <v>2963.304000000001</v>
       </c>
       <c r="G69">
         <v>63.9</v>
@@ -7079,37 +7079,37 @@
         <v>162.1</v>
       </c>
       <c r="M69">
-        <v>688.4713908000001</v>
+        <v>698.7470832000001</v>
       </c>
       <c r="N69">
-        <v>-526.3713908000001</v>
+        <v>-536.6470832000001</v>
       </c>
       <c r="O69">
-        <v>-86.85127948200002</v>
+        <v>-88.54676872800002</v>
       </c>
       <c r="P69">
-        <v>-439.5201113180001</v>
+        <v>-448.1003144720001</v>
       </c>
       <c r="Q69">
-        <v>-392.820111318</v>
+        <v>-401.4003144720001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.237330454912653</v>
+        <v>0.2433157816286734</v>
       </c>
       <c r="T69">
-        <v>3.733285061695866</v>
+        <v>3.849950219873862</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03884910884811162</v>
+        <v>0.03827779842387469</v>
       </c>
       <c r="W69">
-        <v>0.2266393801336153</v>
+        <v>0.2267740951316504</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2354491445340099</v>
+        <v>0.231986657114392</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2320674348106977</v>
+        <v>0.2339674348106978</v>
       </c>
       <c r="C70">
-        <v>-1496.775116054355</v>
+        <v>-1554.516007110279</v>
       </c>
       <c r="D70">
-        <v>1402.628883945645</v>
+        <v>1388.465992889721</v>
       </c>
       <c r="E70">
-        <v>836.9040000000005</v>
+        <v>880.4820000000004</v>
       </c>
       <c r="F70">
-        <v>2963.304000000001</v>
+        <v>3006.882000000001</v>
       </c>
       <c r="G70">
         <v>63.9</v>
@@ -7161,37 +7161,37 @@
         <v>162.1</v>
       </c>
       <c r="M70">
-        <v>698.7470832000001</v>
+        <v>709.0227756000002</v>
       </c>
       <c r="N70">
-        <v>-536.6470832000001</v>
+        <v>-546.9227756000001</v>
       </c>
       <c r="O70">
-        <v>-88.54676872800002</v>
+        <v>-90.24225797400003</v>
       </c>
       <c r="P70">
-        <v>-448.1003144720001</v>
+        <v>-456.6805176260001</v>
       </c>
       <c r="Q70">
-        <v>-401.4003144720001</v>
+        <v>-409.9805176260001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2433157816286734</v>
+        <v>0.2496872584554048</v>
       </c>
       <c r="T70">
-        <v>3.849950219873862</v>
+        <v>3.974142162450438</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03827779842387469</v>
+        <v>0.03772304772207941</v>
       </c>
       <c r="W70">
-        <v>0.2267740951316504</v>
+        <v>0.2269049053471337</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.231986657114392</v>
+        <v>0.2286245316489661</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2339674348106978</v>
+        <v>0.2358674348106977</v>
       </c>
       <c r="C71">
-        <v>-1554.516007110279</v>
+        <v>-1611.973740843298</v>
       </c>
       <c r="D71">
-        <v>1388.465992889721</v>
+        <v>1374.586259156702</v>
       </c>
       <c r="E71">
-        <v>880.4820000000004</v>
+        <v>924.0600000000004</v>
       </c>
       <c r="F71">
-        <v>3006.882000000001</v>
+        <v>3050.46</v>
       </c>
       <c r="G71">
         <v>63.9</v>
@@ -7243,37 +7243,37 @@
         <v>162.1</v>
       </c>
       <c r="M71">
-        <v>709.0227756000002</v>
+        <v>719.2984680000002</v>
       </c>
       <c r="N71">
-        <v>-546.9227756000001</v>
+        <v>-557.1984680000002</v>
       </c>
       <c r="O71">
-        <v>-90.24225797400003</v>
+        <v>-91.93774722000003</v>
       </c>
       <c r="P71">
-        <v>-456.6805176260001</v>
+        <v>-465.2607207800002</v>
       </c>
       <c r="Q71">
-        <v>-409.9805176260001</v>
+        <v>-418.5607207800001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2496872584554048</v>
+        <v>0.2564835004039183</v>
       </c>
       <c r="T71">
-        <v>3.974142162450438</v>
+        <v>4.106613567865452</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03772304772207941</v>
+        <v>0.03718414704033541</v>
       </c>
       <c r="W71">
-        <v>0.2269049053471337</v>
+        <v>0.2270319781278889</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2286245316489661</v>
+        <v>0.2253584669111237</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2358674348106977</v>
+        <v>0.2377674348106977</v>
       </c>
       <c r="C72">
-        <v>-1611.973740843298</v>
+        <v>-1669.156724912462</v>
       </c>
       <c r="D72">
-        <v>1374.586259156702</v>
+        <v>1360.981275087538</v>
       </c>
       <c r="E72">
-        <v>924.0600000000004</v>
+        <v>967.6380000000004</v>
       </c>
       <c r="F72">
-        <v>3050.46</v>
+        <v>3094.038</v>
       </c>
       <c r="G72">
         <v>63.9</v>
@@ -7325,37 +7325,37 @@
         <v>162.1</v>
       </c>
       <c r="M72">
-        <v>719.2984680000002</v>
+        <v>729.5741604000001</v>
       </c>
       <c r="N72">
-        <v>-557.1984680000002</v>
+        <v>-567.4741604000001</v>
       </c>
       <c r="O72">
-        <v>-91.93774722000003</v>
+        <v>-93.63323646600001</v>
       </c>
       <c r="P72">
-        <v>-465.2607207800002</v>
+        <v>-473.840923934</v>
       </c>
       <c r="Q72">
-        <v>-418.5607207800001</v>
+        <v>-427.1409239340001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2564835004039183</v>
+        <v>0.2637484486937086</v>
       </c>
       <c r="T72">
-        <v>4.106613567865452</v>
+        <v>4.248220932274606</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03718414704033541</v>
+        <v>0.03666042665948561</v>
       </c>
       <c r="W72">
-        <v>0.2270319781278889</v>
+        <v>0.2271554713936933</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2253584669111237</v>
+        <v>0.2221844039968826</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2377674348106977</v>
+        <v>0.2396674348106977</v>
       </c>
       <c r="C73">
-        <v>-1669.156724912462</v>
+        <v>-1726.073037379387</v>
       </c>
       <c r="D73">
-        <v>1360.981275087538</v>
+        <v>1347.642962620613</v>
       </c>
       <c r="E73">
-        <v>967.6379999999999</v>
+        <v>1011.216</v>
       </c>
       <c r="F73">
-        <v>3094.038</v>
+        <v>3137.616</v>
       </c>
       <c r="G73">
         <v>63.9</v>
@@ -7407,37 +7407,37 @@
         <v>162.1</v>
       </c>
       <c r="M73">
-        <v>729.5741604</v>
+        <v>739.8498528</v>
       </c>
       <c r="N73">
-        <v>-567.4741604</v>
+        <v>-577.7498528</v>
       </c>
       <c r="O73">
-        <v>-93.633236466</v>
+        <v>-95.32872571200001</v>
       </c>
       <c r="P73">
-        <v>-473.840923934</v>
+        <v>-482.421127088</v>
       </c>
       <c r="Q73">
-        <v>-427.1409239339999</v>
+        <v>-435.721127088</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2637484486937086</v>
+        <v>0.271532321861341</v>
       </c>
       <c r="T73">
-        <v>4.248220932274605</v>
+        <v>4.399943108427268</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03666042665948562</v>
+        <v>0.03615125406699277</v>
       </c>
       <c r="W73">
-        <v>0.2271554713936933</v>
+        <v>0.2272755342910031</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2221844039968826</v>
+        <v>0.2190985094969259</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2396674348106977</v>
+        <v>0.2415674348106977</v>
       </c>
       <c r="C74">
-        <v>-1726.073037379387</v>
+        <v>-1782.730442702622</v>
       </c>
       <c r="D74">
-        <v>1347.642962620613</v>
+        <v>1334.563557297378</v>
       </c>
       <c r="E74">
-        <v>1011.216</v>
+        <v>1054.794</v>
       </c>
       <c r="F74">
-        <v>3137.616</v>
+        <v>3181.194</v>
       </c>
       <c r="G74">
         <v>63.9</v>
@@ -7489,37 +7489,37 @@
         <v>162.1</v>
       </c>
       <c r="M74">
-        <v>739.8498528</v>
+        <v>750.1255452</v>
       </c>
       <c r="N74">
-        <v>-577.7498528</v>
+        <v>-588.0255452</v>
       </c>
       <c r="O74">
-        <v>-95.32872571200001</v>
+        <v>-97.024214958</v>
       </c>
       <c r="P74">
-        <v>-482.421127088</v>
+        <v>-491.001330242</v>
       </c>
       <c r="Q74">
-        <v>-435.721127088</v>
+        <v>-444.3013302419999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.271532321861341</v>
+        <v>0.2798927782265758</v>
       </c>
       <c r="T74">
-        <v>4.399943108427268</v>
+        <v>4.562903964294946</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03615125406699277</v>
+        <v>0.03565603140854081</v>
       </c>
       <c r="W74">
-        <v>0.2272755342910031</v>
+        <v>0.2273923077938661</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2190985094969259</v>
+        <v>0.2160971600517625</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2415674348106977</v>
+        <v>0.2434674348106977</v>
       </c>
       <c r="C75">
-        <v>-1782.730442702622</v>
+        <v>-1839.136406809574</v>
       </c>
       <c r="D75">
-        <v>1334.563557297378</v>
+        <v>1321.735593190426</v>
       </c>
       <c r="E75">
-        <v>1054.794</v>
+        <v>1098.372</v>
       </c>
       <c r="F75">
-        <v>3181.194</v>
+        <v>3224.772</v>
       </c>
       <c r="G75">
         <v>63.9</v>
@@ -7571,37 +7571,37 @@
         <v>162.1</v>
       </c>
       <c r="M75">
-        <v>750.1255452</v>
+        <v>760.4012376000001</v>
       </c>
       <c r="N75">
-        <v>-588.0255452</v>
+        <v>-598.3012376</v>
       </c>
       <c r="O75">
-        <v>-97.024214958</v>
+        <v>-98.71970420400001</v>
       </c>
       <c r="P75">
-        <v>-491.001330242</v>
+        <v>-499.5815333960001</v>
       </c>
       <c r="Q75">
-        <v>-444.3013302419999</v>
+        <v>-452.881533396</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2798927782265758</v>
+        <v>0.2888963466199057</v>
       </c>
       <c r="T75">
-        <v>4.562903964294946</v>
+        <v>4.738400270613982</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03565603140854081</v>
+        <v>0.03517419314626323</v>
       </c>
       <c r="W75">
-        <v>0.2273923077938661</v>
+        <v>0.2275059252561111</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2160971600517625</v>
+        <v>0.2131769281591711</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2434674348106977</v>
+        <v>0.2453674348106977</v>
       </c>
       <c r="C76">
-        <v>-1839.136406809574</v>
+        <v>-1895.298111307475</v>
       </c>
       <c r="D76">
-        <v>1321.735593190426</v>
+        <v>1309.151888692525</v>
       </c>
       <c r="E76">
-        <v>1098.372</v>
+        <v>1141.95</v>
       </c>
       <c r="F76">
-        <v>3224.772</v>
+        <v>3268.35</v>
       </c>
       <c r="G76">
         <v>63.9</v>
@@ -7653,37 +7653,37 @@
         <v>162.1</v>
       </c>
       <c r="M76">
-        <v>760.4012376000001</v>
+        <v>770.6769300000001</v>
       </c>
       <c r="N76">
-        <v>-598.3012376</v>
+        <v>-608.5769300000001</v>
       </c>
       <c r="O76">
-        <v>-98.71970420400001</v>
+        <v>-100.41519345</v>
       </c>
       <c r="P76">
-        <v>-499.5815333960001</v>
+        <v>-508.1617365500001</v>
       </c>
       <c r="Q76">
-        <v>-452.881533396</v>
+        <v>-461.4617365500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2888963466199057</v>
+        <v>0.2986202004847019</v>
       </c>
       <c r="T76">
-        <v>4.738400270613982</v>
+        <v>4.927936281438542</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03517419314626323</v>
+        <v>0.03470520390431305</v>
       </c>
       <c r="W76">
-        <v>0.2275059252561111</v>
+        <v>0.227616512919363</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2131769281591711</v>
+        <v>0.2103345691170488</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2453674348106977</v>
+        <v>0.2472674348106977</v>
       </c>
       <c r="C77">
-        <v>-1895.298111307475</v>
+        <v>-1951.222466890218</v>
       </c>
       <c r="D77">
-        <v>1309.151888692525</v>
+        <v>1296.805533109783</v>
       </c>
       <c r="E77">
-        <v>1141.95</v>
+        <v>1185.528</v>
       </c>
       <c r="F77">
-        <v>3268.35</v>
+        <v>3311.928</v>
       </c>
       <c r="G77">
         <v>63.9</v>
@@ -7735,37 +7735,37 @@
         <v>162.1</v>
       </c>
       <c r="M77">
-        <v>770.6769300000001</v>
+        <v>780.9526224000001</v>
       </c>
       <c r="N77">
-        <v>-608.5769300000001</v>
+        <v>-618.8526224000001</v>
       </c>
       <c r="O77">
-        <v>-100.41519345</v>
+        <v>-102.110682696</v>
       </c>
       <c r="P77">
-        <v>-508.1617365500001</v>
+        <v>-516.7419397040001</v>
       </c>
       <c r="Q77">
-        <v>-461.4617365500001</v>
+        <v>-470.041939704</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2986202004847019</v>
+        <v>0.3091543755048979</v>
       </c>
       <c r="T77">
-        <v>4.927936281438542</v>
+        <v>5.133266959831816</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03470520390431305</v>
+        <v>0.03424855648451946</v>
       </c>
       <c r="W77">
-        <v>0.227616512919363</v>
+        <v>0.2277241903809503</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2103345691170488</v>
+        <v>0.2075670089970877</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2472674348106977</v>
+        <v>0.2491674348106978</v>
       </c>
       <c r="C78">
-        <v>-1951.222466890218</v>
+        <v>-2006.916125993663</v>
       </c>
       <c r="D78">
-        <v>1296.805533109783</v>
+        <v>1284.689874006337</v>
       </c>
       <c r="E78">
-        <v>1185.528</v>
+        <v>1229.106</v>
       </c>
       <c r="F78">
-        <v>3311.928</v>
+        <v>3355.506</v>
       </c>
       <c r="G78">
         <v>63.9</v>
@@ -7817,37 +7817,37 @@
         <v>162.1</v>
       </c>
       <c r="M78">
-        <v>780.9526224000001</v>
+        <v>791.2283148000001</v>
       </c>
       <c r="N78">
-        <v>-618.8526224000001</v>
+        <v>-629.1283148000001</v>
       </c>
       <c r="O78">
-        <v>-102.110682696</v>
+        <v>-103.806171942</v>
       </c>
       <c r="P78">
-        <v>-516.7419397040001</v>
+        <v>-525.3221428580001</v>
       </c>
       <c r="Q78">
-        <v>-470.041939704</v>
+        <v>-478.6221428580001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3091543755048979</v>
+        <v>0.3206045657442413</v>
       </c>
       <c r="T78">
-        <v>5.133266959831816</v>
+        <v>5.356452479824503</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03424855648451946</v>
+        <v>0.03380377003666855</v>
       </c>
       <c r="W78">
-        <v>0.2277241903809503</v>
+        <v>0.2278290710253536</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2075670089970877</v>
+        <v>0.2048713335555671</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2491674348106978</v>
+        <v>0.2510674348106978</v>
       </c>
       <c r="C79">
-        <v>-2006.916125993663</v>
+        <v>-2062.385494748103</v>
       </c>
       <c r="D79">
-        <v>1284.689874006337</v>
+        <v>1272.798505251897</v>
       </c>
       <c r="E79">
-        <v>1229.106</v>
+        <v>1272.684</v>
       </c>
       <c r="F79">
-        <v>3355.506</v>
+        <v>3399.084</v>
       </c>
       <c r="G79">
         <v>63.9</v>
@@ -7899,37 +7899,37 @@
         <v>162.1</v>
       </c>
       <c r="M79">
-        <v>791.2283148000001</v>
+        <v>801.5040072</v>
       </c>
       <c r="N79">
-        <v>-629.1283148000001</v>
+        <v>-639.4040072</v>
       </c>
       <c r="O79">
-        <v>-103.806171942</v>
+        <v>-105.501661188</v>
       </c>
       <c r="P79">
-        <v>-525.3221428580001</v>
+        <v>-533.902346012</v>
       </c>
       <c r="Q79">
-        <v>-478.6221428580001</v>
+        <v>-487.2023460119999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3206045657442413</v>
+        <v>0.3330956823689795</v>
       </c>
       <c r="T79">
-        <v>5.356452479824503</v>
+        <v>5.599927592543798</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03380377003666855</v>
+        <v>0.03337038836953178</v>
       </c>
       <c r="W79">
-        <v>0.2278290710253536</v>
+        <v>0.2279312624224644</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2048713335555671</v>
+        <v>0.2022447779971623</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2510674348106978</v>
+        <v>0.2529674348106977</v>
       </c>
       <c r="C80">
-        <v>-2062.385494748103</v>
+        <v>-2117.636744273002</v>
       </c>
       <c r="D80">
-        <v>1272.798505251897</v>
+        <v>1261.125255726997</v>
       </c>
       <c r="E80">
-        <v>1272.684</v>
+        <v>1316.262</v>
       </c>
       <c r="F80">
-        <v>3399.084</v>
+        <v>3442.662</v>
       </c>
       <c r="G80">
         <v>63.9</v>
@@ -7981,37 +7981,37 @@
         <v>162.1</v>
       </c>
       <c r="M80">
-        <v>801.5040072</v>
+        <v>811.7796996000001</v>
       </c>
       <c r="N80">
-        <v>-639.4040072</v>
+        <v>-649.6796996</v>
       </c>
       <c r="O80">
-        <v>-105.501661188</v>
+        <v>-107.197150434</v>
       </c>
       <c r="P80">
-        <v>-533.902346012</v>
+        <v>-542.482549166</v>
       </c>
       <c r="Q80">
-        <v>-487.2023460119999</v>
+        <v>-495.782549166</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3330956823689795</v>
+        <v>0.3467764291484547</v>
       </c>
       <c r="T80">
-        <v>5.599927592543798</v>
+        <v>5.86659081123636</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03337038836953178</v>
+        <v>0.03294797839017062</v>
       </c>
       <c r="W80">
-        <v>0.2279312624224644</v>
+        <v>0.2280308666955978</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2022447779971623</v>
+        <v>0.1996847175161856</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2529674348106977</v>
+        <v>0.2548674348106977</v>
       </c>
       <c r="C81">
-        <v>-2117.636744273002</v>
+        <v>-2172.675821355863</v>
       </c>
       <c r="D81">
-        <v>1261.125255726997</v>
+        <v>1249.664178644137</v>
       </c>
       <c r="E81">
-        <v>1316.262</v>
+        <v>1359.84</v>
       </c>
       <c r="F81">
-        <v>3442.662</v>
+        <v>3486.24</v>
       </c>
       <c r="G81">
         <v>63.9</v>
@@ -8063,37 +8063,37 @@
         <v>162.1</v>
       </c>
       <c r="M81">
-        <v>811.7796996000001</v>
+        <v>822.0553920000001</v>
       </c>
       <c r="N81">
-        <v>-649.6796996</v>
+        <v>-659.9553920000001</v>
       </c>
       <c r="O81">
-        <v>-107.197150434</v>
+        <v>-108.89263968</v>
       </c>
       <c r="P81">
-        <v>-542.482549166</v>
+        <v>-551.0627523200001</v>
       </c>
       <c r="Q81">
-        <v>-495.782549166</v>
+        <v>-504.36275232</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3467764291484547</v>
+        <v>0.3618252506058775</v>
       </c>
       <c r="T81">
-        <v>5.86659081123636</v>
+        <v>6.159920351798179</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03294797839017062</v>
+        <v>0.03253612866029348</v>
       </c>
       <c r="W81">
-        <v>0.2280308666955978</v>
+        <v>0.2281279808619028</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1996847175161856</v>
+        <v>0.1971886585472333</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2548674348106977</v>
+        <v>0.2567674348106977</v>
       </c>
       <c r="C82">
-        <v>-2172.675821355863</v>
+        <v>-2227.508458554037</v>
       </c>
       <c r="D82">
-        <v>1249.664178644137</v>
+        <v>1238.409541445963</v>
       </c>
       <c r="E82">
-        <v>1359.84</v>
+        <v>1403.418</v>
       </c>
       <c r="F82">
-        <v>3486.24</v>
+        <v>3529.818</v>
       </c>
       <c r="G82">
         <v>63.9</v>
@@ -8145,37 +8145,37 @@
         <v>162.1</v>
       </c>
       <c r="M82">
-        <v>822.0553920000001</v>
+        <v>832.3310844000001</v>
       </c>
       <c r="N82">
-        <v>-659.9553920000001</v>
+        <v>-670.2310844000001</v>
       </c>
       <c r="O82">
-        <v>-108.89263968</v>
+        <v>-110.588128926</v>
       </c>
       <c r="P82">
-        <v>-551.0627523200001</v>
+        <v>-559.642955474</v>
       </c>
       <c r="Q82">
-        <v>-504.36275232</v>
+        <v>-512.942955474</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3618252506058775</v>
+        <v>0.3784581585325026</v>
       </c>
       <c r="T82">
-        <v>6.159920351798179</v>
+        <v>6.484126686103346</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03253612866029348</v>
+        <v>0.03213444805954913</v>
       </c>
       <c r="W82">
-        <v>0.2281279808619028</v>
+        <v>0.2282226971475583</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1971886585472333</v>
+        <v>0.194754230663934</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2567674348106977</v>
+        <v>0.2586674348106978</v>
       </c>
       <c r="C83">
-        <v>-2227.508458554037</v>
+        <v>-2282.140183755546</v>
       </c>
       <c r="D83">
-        <v>1238.409541445963</v>
+        <v>1227.355816244455</v>
       </c>
       <c r="E83">
-        <v>1403.418</v>
+        <v>1446.996000000001</v>
       </c>
       <c r="F83">
-        <v>3529.818</v>
+        <v>3573.396000000001</v>
       </c>
       <c r="G83">
         <v>63.9</v>
@@ -8227,37 +8227,37 @@
         <v>162.1</v>
       </c>
       <c r="M83">
-        <v>832.3310844000001</v>
+        <v>842.6067768000001</v>
       </c>
       <c r="N83">
-        <v>-670.2310844000001</v>
+        <v>-680.5067768000001</v>
       </c>
       <c r="O83">
-        <v>-110.588128926</v>
+        <v>-112.283618172</v>
       </c>
       <c r="P83">
-        <v>-559.642955474</v>
+        <v>-568.2231586280001</v>
       </c>
       <c r="Q83">
-        <v>-512.942955474</v>
+        <v>-521.523158628</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3784581585325026</v>
+        <v>0.3969391673398638</v>
       </c>
       <c r="T83">
-        <v>6.484126686103346</v>
+        <v>6.844355946442421</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03213444805954913</v>
+        <v>0.03174256454662779</v>
       </c>
       <c r="W83">
-        <v>0.2282226971475583</v>
+        <v>0.2283151032799052</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.194754230663934</v>
+        <v>0.1923791790704715</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2586674348106978</v>
+        <v>0.2605674348106978</v>
       </c>
       <c r="C84">
-        <v>-2282.140183755546</v>
+        <v>-2336.576329232395</v>
       </c>
       <c r="D84">
-        <v>1227.355816244455</v>
+        <v>1216.497670767605</v>
       </c>
       <c r="E84">
-        <v>1446.996000000001</v>
+        <v>1490.574000000001</v>
       </c>
       <c r="F84">
-        <v>3573.396000000001</v>
+        <v>3616.974000000001</v>
       </c>
       <c r="G84">
         <v>63.9</v>
@@ -8309,37 +8309,37 @@
         <v>162.1</v>
       </c>
       <c r="M84">
-        <v>842.6067768000001</v>
+        <v>852.8824692000002</v>
       </c>
       <c r="N84">
-        <v>-680.5067768000001</v>
+        <v>-690.7824692000002</v>
       </c>
       <c r="O84">
-        <v>-112.283618172</v>
+        <v>-113.979107418</v>
       </c>
       <c r="P84">
-        <v>-568.2231586280001</v>
+        <v>-576.8033617820001</v>
       </c>
       <c r="Q84">
-        <v>-521.523158628</v>
+        <v>-530.1033617820001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3969391673398638</v>
+        <v>0.417594412477503</v>
       </c>
       <c r="T84">
-        <v>6.844355946442421</v>
+        <v>7.246965119762565</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03174256454662779</v>
+        <v>0.03136012400992143</v>
       </c>
       <c r="W84">
-        <v>0.2283151032799052</v>
+        <v>0.2284052827584606</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1923791790704715</v>
+        <v>0.1900613576358875</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2605674348106978</v>
+        <v>0.2624674348106977</v>
       </c>
       <c r="C85">
-        <v>-2336.576329232395</v>
+        <v>-2390.822040217564</v>
       </c>
       <c r="D85">
-        <v>1216.497670767605</v>
+        <v>1205.829959782436</v>
       </c>
       <c r="E85">
-        <v>1490.574000000001</v>
+        <v>1534.152</v>
       </c>
       <c r="F85">
-        <v>3616.974000000001</v>
+        <v>3660.552000000001</v>
       </c>
       <c r="G85">
         <v>63.9</v>
@@ -8391,37 +8391,37 @@
         <v>162.1</v>
       </c>
       <c r="M85">
-        <v>852.8824692000002</v>
+        <v>863.1581616000002</v>
       </c>
       <c r="N85">
-        <v>-690.7824692000002</v>
+        <v>-701.0581616000002</v>
       </c>
       <c r="O85">
-        <v>-113.979107418</v>
+        <v>-115.674596664</v>
       </c>
       <c r="P85">
-        <v>-576.8033617820001</v>
+        <v>-585.3835649360001</v>
       </c>
       <c r="Q85">
-        <v>-530.1033617820001</v>
+        <v>-538.683564936</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.417594412477503</v>
+        <v>0.440831563257347</v>
       </c>
       <c r="T85">
-        <v>7.246965119762565</v>
+        <v>7.699900439747726</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03136012400992143</v>
+        <v>0.03098678920027951</v>
       </c>
       <c r="W85">
-        <v>0.2284052827584606</v>
+        <v>0.2284933151065741</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1900613576358875</v>
+        <v>0.1877987224259364</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2624674348106977</v>
+        <v>0.2643674348106977</v>
       </c>
       <c r="C86">
-        <v>-2390.822040217564</v>
+        <v>-2444.882283034618</v>
       </c>
       <c r="D86">
-        <v>1205.829959782436</v>
+        <v>1195.347716965382</v>
       </c>
       <c r="E86">
-        <v>1534.152</v>
+        <v>1577.73</v>
       </c>
       <c r="F86">
-        <v>3660.552</v>
+        <v>3704.13</v>
       </c>
       <c r="G86">
         <v>63.9</v>
@@ -8473,37 +8473,37 @@
         <v>162.1</v>
       </c>
       <c r="M86">
-        <v>863.1581616000001</v>
+        <v>873.4338540000001</v>
       </c>
       <c r="N86">
-        <v>-701.0581616000001</v>
+        <v>-711.3338540000001</v>
       </c>
       <c r="O86">
-        <v>-115.674596664</v>
+        <v>-117.37008591</v>
       </c>
       <c r="P86">
-        <v>-585.3835649360001</v>
+        <v>-593.96376809</v>
       </c>
       <c r="Q86">
-        <v>-538.683564936</v>
+        <v>-547.26376809</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4408315632573467</v>
+        <v>0.4671670008078365</v>
       </c>
       <c r="T86">
-        <v>7.69990043974772</v>
+        <v>8.213227135730902</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03098678920027951</v>
+        <v>0.03062223873909975</v>
       </c>
       <c r="W86">
-        <v>0.2284933151065741</v>
+        <v>0.2285792761053203</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1877987224259364</v>
+        <v>0.1855893256915137</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2643674348106977</v>
+        <v>0.2662674348106978</v>
       </c>
       <c r="C87">
-        <v>-2444.882283034618</v>
+        <v>-2498.761852806972</v>
       </c>
       <c r="D87">
-        <v>1195.347716965382</v>
+        <v>1185.046147193027</v>
       </c>
       <c r="E87">
-        <v>1577.73</v>
+        <v>1621.308</v>
       </c>
       <c r="F87">
-        <v>3704.13</v>
+        <v>3747.708</v>
       </c>
       <c r="G87">
         <v>63.9</v>
@@ -8555,37 +8555,37 @@
         <v>162.1</v>
       </c>
       <c r="M87">
-        <v>873.4338540000001</v>
+        <v>883.7095464</v>
       </c>
       <c r="N87">
-        <v>-711.3338540000001</v>
+        <v>-721.6095464</v>
       </c>
       <c r="O87">
-        <v>-117.37008591</v>
+        <v>-119.065575156</v>
       </c>
       <c r="P87">
-        <v>-593.96376809</v>
+        <v>-602.543971244</v>
       </c>
       <c r="Q87">
-        <v>-547.26376809</v>
+        <v>-555.8439712439999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4671670008078365</v>
+        <v>0.497264643722682</v>
       </c>
       <c r="T87">
-        <v>8.213227135730902</v>
+        <v>8.799886216854539</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03062223873909975</v>
+        <v>0.03026616619562185</v>
       </c>
       <c r="W87">
-        <v>0.2285792761053203</v>
+        <v>0.2286632380110724</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1855893256915137</v>
+        <v>0.1834313102764961</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2662674348106978</v>
+        <v>0.2681674348106977</v>
       </c>
       <c r="C88">
-        <v>-2498.761852806972</v>
+        <v>-2552.465380771908</v>
       </c>
       <c r="D88">
-        <v>1185.046147193027</v>
+        <v>1174.920619228092</v>
       </c>
       <c r="E88">
-        <v>1621.308</v>
+        <v>1664.886</v>
       </c>
       <c r="F88">
-        <v>3747.708</v>
+        <v>3791.286</v>
       </c>
       <c r="G88">
         <v>63.9</v>
@@ -8637,37 +8637,37 @@
         <v>162.1</v>
       </c>
       <c r="M88">
-        <v>883.7095464</v>
+        <v>893.9852388</v>
       </c>
       <c r="N88">
-        <v>-721.6095464</v>
+        <v>-731.8852388</v>
       </c>
       <c r="O88">
-        <v>-119.065575156</v>
+        <v>-120.761064402</v>
       </c>
       <c r="P88">
-        <v>-602.543971244</v>
+        <v>-611.124174398</v>
       </c>
       <c r="Q88">
-        <v>-555.8439712439999</v>
+        <v>-564.424174398</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.497264643722682</v>
+        <v>0.5319926932398114</v>
       </c>
       <c r="T88">
-        <v>8.799886216854539</v>
+        <v>9.476800541227965</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03026616619562185</v>
+        <v>0.02991827922785608</v>
       </c>
       <c r="W88">
-        <v>0.2286632380110724</v>
+        <v>0.2287452697580716</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1834313102764961</v>
+        <v>0.181322904411249</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2681674348106977</v>
+        <v>0.2700674348106977</v>
       </c>
       <c r="C89">
-        <v>-2552.465380771908</v>
+        <v>-2605.997341222821</v>
       </c>
       <c r="D89">
-        <v>1174.920619228092</v>
+        <v>1164.966658777179</v>
       </c>
       <c r="E89">
-        <v>1664.886</v>
+        <v>1708.464</v>
       </c>
       <c r="F89">
-        <v>3791.286</v>
+        <v>3834.864</v>
       </c>
       <c r="G89">
         <v>63.9</v>
@@ -8719,37 +8719,37 @@
         <v>162.1</v>
       </c>
       <c r="M89">
-        <v>893.9852388</v>
+        <v>904.2609312000001</v>
       </c>
       <c r="N89">
-        <v>-731.8852388</v>
+        <v>-742.1609312000001</v>
       </c>
       <c r="O89">
-        <v>-120.761064402</v>
+        <v>-122.456553648</v>
       </c>
       <c r="P89">
-        <v>-611.124174398</v>
+        <v>-619.7043775520001</v>
       </c>
       <c r="Q89">
-        <v>-564.424174398</v>
+        <v>-573.0043775520001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5319926932398114</v>
+        <v>0.5725087510097958</v>
       </c>
       <c r="T89">
-        <v>9.476800541227965</v>
+        <v>10.26653391966363</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02991827922785608</v>
+        <v>0.02957829878208499</v>
       </c>
       <c r="W89">
-        <v>0.2287452697580716</v>
+        <v>0.2288254371471844</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.181322904411249</v>
+        <v>0.1792624168611212</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2700674348106977</v>
+        <v>0.2719674348106977</v>
       </c>
       <c r="C90">
-        <v>-2605.997341222821</v>
+        <v>-2659.362058101533</v>
       </c>
       <c r="D90">
-        <v>1164.966658777179</v>
+        <v>1155.179941898467</v>
       </c>
       <c r="E90">
-        <v>1708.464</v>
+        <v>1752.042</v>
       </c>
       <c r="F90">
-        <v>3834.864</v>
+        <v>3878.442</v>
       </c>
       <c r="G90">
         <v>63.9</v>
@@ -8801,37 +8801,37 @@
         <v>162.1</v>
       </c>
       <c r="M90">
-        <v>904.2609312000001</v>
+        <v>914.5366236</v>
       </c>
       <c r="N90">
-        <v>-742.1609312000001</v>
+        <v>-752.4366236</v>
       </c>
       <c r="O90">
-        <v>-122.456553648</v>
+        <v>-124.152042894</v>
       </c>
       <c r="P90">
-        <v>-619.7043775520001</v>
+        <v>-628.2845807059999</v>
       </c>
       <c r="Q90">
-        <v>-573.0043775520001</v>
+        <v>-581.5845807059999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5725087510097958</v>
+        <v>0.620391364737959</v>
       </c>
       <c r="T90">
-        <v>10.26653391966363</v>
+        <v>11.1998551850876</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02957829878208499</v>
+        <v>0.02924595834633123</v>
       </c>
       <c r="W90">
-        <v>0.2288254371471844</v>
+        <v>0.2289038030219351</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1792624168611212</v>
+        <v>0.1772482324020075</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2719674348106977</v>
+        <v>0.2738674348106977</v>
       </c>
       <c r="C91">
-        <v>-2659.362058101533</v>
+        <v>-2712.563711261085</v>
       </c>
       <c r="D91">
-        <v>1155.179941898467</v>
+        <v>1145.556288738915</v>
       </c>
       <c r="E91">
-        <v>1752.042</v>
+        <v>1795.62</v>
       </c>
       <c r="F91">
-        <v>3878.442</v>
+        <v>3922.02</v>
       </c>
       <c r="G91">
         <v>63.9</v>
@@ -8883,37 +8883,37 @@
         <v>162.1</v>
       </c>
       <c r="M91">
-        <v>914.5366236</v>
+        <v>924.8123160000001</v>
       </c>
       <c r="N91">
-        <v>-752.4366236</v>
+        <v>-762.7123160000001</v>
       </c>
       <c r="O91">
-        <v>-124.152042894</v>
+        <v>-125.84753214</v>
       </c>
       <c r="P91">
-        <v>-628.2845807059999</v>
+        <v>-636.8647838600001</v>
       </c>
       <c r="Q91">
-        <v>-581.5845807059999</v>
+        <v>-590.1647838600001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.620391364737959</v>
+        <v>0.6778505012117548</v>
       </c>
       <c r="T91">
-        <v>11.1998551850876</v>
+        <v>12.31984070359636</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02924595834633123</v>
+        <v>0.02892100325359421</v>
       </c>
       <c r="W91">
-        <v>0.2289038030219351</v>
+        <v>0.2289804274328025</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1772482324020075</v>
+        <v>0.1752788075975407</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2738674348106977</v>
+        <v>0.2757674348106977</v>
       </c>
       <c r="C92">
-        <v>-2712.563711261085</v>
+        <v>-2765.606342418082</v>
       </c>
       <c r="D92">
-        <v>1145.556288738915</v>
+        <v>1136.091657581918</v>
       </c>
       <c r="E92">
-        <v>1795.62</v>
+        <v>1839.198</v>
       </c>
       <c r="F92">
-        <v>3922.02</v>
+        <v>3965.598</v>
       </c>
       <c r="G92">
         <v>63.9</v>
@@ -8965,37 +8965,37 @@
         <v>162.1</v>
       </c>
       <c r="M92">
-        <v>924.8123160000001</v>
+        <v>935.0880084000001</v>
       </c>
       <c r="N92">
-        <v>-762.7123160000001</v>
+        <v>-772.9880084000001</v>
       </c>
       <c r="O92">
-        <v>-125.84753214</v>
+        <v>-127.543021386</v>
       </c>
       <c r="P92">
-        <v>-636.8647838600001</v>
+        <v>-645.4449870140002</v>
       </c>
       <c r="Q92">
-        <v>-590.1647838600001</v>
+        <v>-598.7449870140001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6778505012117548</v>
+        <v>0.7480783346797276</v>
       </c>
       <c r="T92">
-        <v>12.31984070359636</v>
+        <v>13.68871189288484</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02892100325359421</v>
+        <v>0.02860319003102724</v>
       </c>
       <c r="W92">
-        <v>0.2289804274328025</v>
+        <v>0.2290553677906838</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1752788075975407</v>
+        <v>0.1733526668547105</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2757674348106977</v>
+        <v>0.2776674348106978</v>
       </c>
       <c r="C93">
-        <v>-2765.606342418082</v>
+        <v>-2818.493860812367</v>
       </c>
       <c r="D93">
-        <v>1136.091657581918</v>
+        <v>1126.782139187634</v>
       </c>
       <c r="E93">
-        <v>1839.198</v>
+        <v>1882.776</v>
       </c>
       <c r="F93">
-        <v>3965.598</v>
+        <v>4009.176</v>
       </c>
       <c r="G93">
         <v>63.9</v>
@@ -9047,37 +9047,37 @@
         <v>162.1</v>
       </c>
       <c r="M93">
-        <v>935.0880084000001</v>
+        <v>945.3637008000002</v>
       </c>
       <c r="N93">
-        <v>-772.9880084000001</v>
+        <v>-783.2637008000002</v>
       </c>
       <c r="O93">
-        <v>-127.543021386</v>
+        <v>-129.238510632</v>
       </c>
       <c r="P93">
-        <v>-645.4449870140002</v>
+        <v>-654.0251901680001</v>
       </c>
       <c r="Q93">
-        <v>-598.7449870140001</v>
+        <v>-607.3251901680001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7480783346797276</v>
+        <v>0.835863126514694</v>
       </c>
       <c r="T93">
-        <v>13.68871189288484</v>
+        <v>15.39980087949545</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02860319003102724</v>
+        <v>0.02829228579155955</v>
       </c>
       <c r="W93">
-        <v>0.2290553677906838</v>
+        <v>0.2291286790103503</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1733526668547105</v>
+        <v>0.1714683987367246</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2776674348106978</v>
+        <v>0.2795674348106977</v>
       </c>
       <c r="C94">
-        <v>-2818.493860812367</v>
+        <v>-2871.230048590703</v>
       </c>
       <c r="D94">
-        <v>1126.782139187634</v>
+        <v>1117.623951409297</v>
       </c>
       <c r="E94">
-        <v>1882.776</v>
+        <v>1926.354</v>
       </c>
       <c r="F94">
-        <v>4009.176</v>
+        <v>4052.754</v>
       </c>
       <c r="G94">
         <v>63.9</v>
@@ -9129,37 +9129,37 @@
         <v>162.1</v>
       </c>
       <c r="M94">
-        <v>945.3637008000002</v>
+        <v>955.6393932000001</v>
       </c>
       <c r="N94">
-        <v>-783.2637008000002</v>
+        <v>-793.5393932000001</v>
       </c>
       <c r="O94">
-        <v>-129.238510632</v>
+        <v>-130.933999878</v>
       </c>
       <c r="P94">
-        <v>-654.0251901680001</v>
+        <v>-662.6053933220001</v>
       </c>
       <c r="Q94">
-        <v>-607.3251901680001</v>
+        <v>-615.905393322</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.835863126514694</v>
+        <v>0.9487292874453647</v>
       </c>
       <c r="T94">
-        <v>15.39980087949545</v>
+        <v>17.59977243370909</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02829228579155955</v>
+        <v>0.02798806766476859</v>
       </c>
       <c r="W94">
-        <v>0.2291286790103503</v>
+        <v>0.2292004136446476</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1714683987367246</v>
+        <v>0.169624652513749</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2795674348106977</v>
+        <v>0.2814674348106978</v>
       </c>
       <c r="C95">
-        <v>-2871.230048590703</v>
+        <v>-2923.818565930036</v>
       </c>
       <c r="D95">
-        <v>1117.623951409297</v>
+        <v>1108.613434069965</v>
       </c>
       <c r="E95">
-        <v>1926.354</v>
+        <v>1969.932</v>
       </c>
       <c r="F95">
-        <v>4052.754</v>
+        <v>4096.332</v>
       </c>
       <c r="G95">
         <v>63.9</v>
@@ -9211,37 +9211,37 @@
         <v>162.1</v>
       </c>
       <c r="M95">
-        <v>955.6393932000001</v>
+        <v>965.9150856000001</v>
       </c>
       <c r="N95">
-        <v>-793.5393932000001</v>
+        <v>-803.8150856000001</v>
       </c>
       <c r="O95">
-        <v>-130.933999878</v>
+        <v>-132.629489124</v>
       </c>
       <c r="P95">
-        <v>-662.6053933220001</v>
+        <v>-671.185596476</v>
       </c>
       <c r="Q95">
-        <v>-615.905393322</v>
+        <v>-624.485596476</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9487292874453647</v>
+        <v>1.099217502019593</v>
       </c>
       <c r="T95">
-        <v>17.59977243370909</v>
+        <v>20.53306783932728</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02798806766476859</v>
+        <v>0.02769032226407956</v>
       </c>
       <c r="W95">
-        <v>0.2292004136446476</v>
+        <v>0.2292706220101301</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.169624652513749</v>
+        <v>0.1678201349338155</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2814674348106978</v>
+        <v>0.2833674348106977</v>
       </c>
       <c r="C96">
-        <v>-2923.818565930036</v>
+        <v>-2976.262955914889</v>
       </c>
       <c r="D96">
-        <v>1108.613434069965</v>
+        <v>1099.747044085112</v>
       </c>
       <c r="E96">
-        <v>1969.932</v>
+        <v>2013.510000000001</v>
       </c>
       <c r="F96">
-        <v>4096.332</v>
+        <v>4139.910000000001</v>
       </c>
       <c r="G96">
         <v>63.9</v>
@@ -9293,37 +9293,37 @@
         <v>162.1</v>
       </c>
       <c r="M96">
-        <v>965.9150856000001</v>
+        <v>976.1907780000003</v>
       </c>
       <c r="N96">
-        <v>-803.8150856000001</v>
+        <v>-814.0907780000002</v>
       </c>
       <c r="O96">
-        <v>-132.629489124</v>
+        <v>-134.3249783700001</v>
       </c>
       <c r="P96">
-        <v>-671.185596476</v>
+        <v>-679.7657996300002</v>
       </c>
       <c r="Q96">
-        <v>-624.485596476</v>
+        <v>-633.0657996300001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.099217502019593</v>
+        <v>1.309901002423511</v>
       </c>
       <c r="T96">
-        <v>20.53306783932728</v>
+        <v>24.63968140719274</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02769032226407956</v>
+        <v>0.02739884518761556</v>
       </c>
       <c r="W96">
-        <v>0.2292706220101301</v>
+        <v>0.2293393523047602</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1678201349338155</v>
+        <v>0.1660536071976701</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2833674348106977</v>
+        <v>0.2852674348106977</v>
       </c>
       <c r="C97">
-        <v>-2976.262955914889</v>
+        <v>-3028.566649182591</v>
       </c>
       <c r="D97">
-        <v>1099.747044085112</v>
+        <v>1091.021350817409</v>
       </c>
       <c r="E97">
-        <v>2013.510000000001</v>
+        <v>2057.088</v>
       </c>
       <c r="F97">
-        <v>4139.910000000001</v>
+        <v>4183.488</v>
       </c>
       <c r="G97">
         <v>63.9</v>
@@ -9375,37 +9375,37 @@
         <v>162.1</v>
       </c>
       <c r="M97">
-        <v>976.1907780000003</v>
+        <v>986.4664704000002</v>
       </c>
       <c r="N97">
-        <v>-814.0907780000002</v>
+        <v>-824.3664704000001</v>
       </c>
       <c r="O97">
-        <v>-134.3249783700001</v>
+        <v>-136.020467616</v>
       </c>
       <c r="P97">
-        <v>-679.7657996300002</v>
+        <v>-688.3460027840001</v>
       </c>
       <c r="Q97">
-        <v>-633.0657996300001</v>
+        <v>-641.6460027840001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.309901002423511</v>
+        <v>1.62592625302939</v>
       </c>
       <c r="T97">
-        <v>24.63968140719274</v>
+        <v>30.79960175899094</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02739884518761556</v>
+        <v>0.02711344055024457</v>
       </c>
       <c r="W97">
-        <v>0.2293393523047602</v>
+        <v>0.2294066507182523</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1660536071976701</v>
+        <v>0.1643238821226944</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2852674348106977</v>
+        <v>0.2871674348106977</v>
       </c>
       <c r="C98">
-        <v>-3028.566649182591</v>
+        <v>-3080.732968349088</v>
       </c>
       <c r="D98">
-        <v>1091.021350817409</v>
+        <v>1082.433031650912</v>
       </c>
       <c r="E98">
-        <v>2057.088</v>
+        <v>2100.666</v>
       </c>
       <c r="F98">
-        <v>4183.488</v>
+        <v>4227.066</v>
       </c>
       <c r="G98">
         <v>63.9</v>
@@ -9457,37 +9457,37 @@
         <v>162.1</v>
       </c>
       <c r="M98">
-        <v>986.4664704000002</v>
+        <v>996.7421628</v>
       </c>
       <c r="N98">
-        <v>-824.3664704000001</v>
+        <v>-834.6421627999999</v>
       </c>
       <c r="O98">
-        <v>-136.020467616</v>
+        <v>-137.715956862</v>
       </c>
       <c r="P98">
-        <v>-688.3460027840001</v>
+        <v>-696.926205938</v>
       </c>
       <c r="Q98">
-        <v>-641.6460027840001</v>
+        <v>-650.2262059379999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.625926253029386</v>
+        <v>2.152635004039181</v>
       </c>
       <c r="T98">
-        <v>30.79960175899086</v>
+        <v>41.06613567865449</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02711344055024457</v>
+        <v>0.02683392054457195</v>
       </c>
       <c r="W98">
-        <v>0.2294066507182523</v>
+        <v>0.22947256153559</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1643238821226944</v>
+        <v>0.1626298214822542</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2871674348106977</v>
+        <v>0.2890674348106977</v>
       </c>
       <c r="C99">
-        <v>-3080.732968349088</v>
+        <v>-3132.765132227362</v>
       </c>
       <c r="D99">
-        <v>1082.433031650912</v>
+        <v>1073.978867772638</v>
       </c>
       <c r="E99">
-        <v>2100.666</v>
+        <v>2144.244</v>
       </c>
       <c r="F99">
-        <v>4227.066</v>
+        <v>4270.644</v>
       </c>
       <c r="G99">
         <v>63.9</v>
@@ -9539,37 +9539,37 @@
         <v>162.1</v>
       </c>
       <c r="M99">
-        <v>996.7421628</v>
+        <v>1007.0178552</v>
       </c>
       <c r="N99">
-        <v>-834.6421627999999</v>
+        <v>-844.9178552000001</v>
       </c>
       <c r="O99">
-        <v>-137.715956862</v>
+        <v>-139.411446108</v>
       </c>
       <c r="P99">
-        <v>-696.926205938</v>
+        <v>-705.506409092</v>
       </c>
       <c r="Q99">
-        <v>-650.2262059379999</v>
+        <v>-658.806409092</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.152635004039181</v>
+        <v>3.206052506058771</v>
       </c>
       <c r="T99">
-        <v>41.06613567865449</v>
+        <v>61.59920351798172</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02683392054457195</v>
+        <v>0.02656010502881101</v>
       </c>
       <c r="W99">
-        <v>0.22947256153559</v>
+        <v>0.2295371272342064</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1626298214822542</v>
+        <v>0.1609703335079455</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2890674348106977</v>
+        <v>0.2909674348106978</v>
       </c>
       <c r="C100">
-        <v>-3132.765132227362</v>
+        <v>-3184.666259849689</v>
       </c>
       <c r="D100">
-        <v>1073.978867772638</v>
+        <v>1065.655740150311</v>
       </c>
       <c r="E100">
-        <v>2144.244</v>
+        <v>2187.822</v>
       </c>
       <c r="F100">
-        <v>4270.644</v>
+        <v>4314.222</v>
       </c>
       <c r="G100">
         <v>63.9</v>
@@ -9621,37 +9621,37 @@
         <v>162.1</v>
       </c>
       <c r="M100">
-        <v>1007.0178552</v>
+        <v>1017.2935476</v>
       </c>
       <c r="N100">
-        <v>-844.9178552000001</v>
+        <v>-855.1935476</v>
       </c>
       <c r="O100">
-        <v>-139.411446108</v>
+        <v>-141.106935354</v>
       </c>
       <c r="P100">
-        <v>-705.506409092</v>
+        <v>-714.086612246</v>
       </c>
       <c r="Q100">
-        <v>-658.806409092</v>
+        <v>-667.3866122459999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.206052506058771</v>
+        <v>6.366305012117543</v>
       </c>
       <c r="T100">
-        <v>61.59920351798172</v>
+        <v>123.1984070359634</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02656010502881101</v>
+        <v>0.0262918211396311</v>
       </c>
       <c r="W100">
-        <v>0.2295371272342064</v>
+        <v>0.229600388575275</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1609703335079455</v>
+        <v>0.1593443705432188</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2909674348106978</v>
-      </c>
-      <c r="C101">
-        <v>-3184.666259849689</v>
-      </c>
-      <c r="D101">
-        <v>1065.655740150311</v>
-      </c>
-      <c r="E101">
-        <v>2187.822</v>
-      </c>
-      <c r="F101">
-        <v>4314.222</v>
-      </c>
-      <c r="G101">
-        <v>63.9</v>
-      </c>
-      <c r="H101">
-        <v>2231.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>208.8</v>
-      </c>
-      <c r="K101">
-        <v>46.70000000000002</v>
-      </c>
-      <c r="L101">
-        <v>162.1</v>
-      </c>
-      <c r="M101">
-        <v>1017.2935476</v>
-      </c>
-      <c r="N101">
-        <v>-855.1935476</v>
-      </c>
-      <c r="O101">
-        <v>-141.106935354</v>
-      </c>
-      <c r="P101">
-        <v>-714.086612246</v>
-      </c>
-      <c r="Q101">
-        <v>-667.3866122459999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.366305012117543</v>
-      </c>
-      <c r="T101">
-        <v>123.1984070359634</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0262918211396311</v>
-      </c>
-      <c r="W101">
-        <v>0.229600388575275</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1593443705432188</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
